--- a/wikidata tags/osm_wikidata_keys.xlsx
+++ b/wikidata tags/osm_wikidata_keys.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anwender\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8B20572-2932-4666-B7C3-0B0D23197A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E5E8DE-A67A-43A0-8BBF-8FC9DBACA735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4995" yWindow="2880" windowWidth="21600" windowHeight="11295" xr2:uid="{89892BDC-0D93-43BE-8A63-A12F1562C0D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$781</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2343" uniqueCount="1441">
   <si>
     <t>key</t>
   </si>
@@ -1743,13 +1746,2632 @@
   </si>
   <si>
     <t>Q693369</t>
+  </si>
+  <si>
+    <t>river</t>
+  </si>
+  <si>
+    <t>stream</t>
+  </si>
+  <si>
+    <t>tidal_channel</t>
+  </si>
+  <si>
+    <t>flowline</t>
+  </si>
+  <si>
+    <t>canal</t>
+  </si>
+  <si>
+    <t>pressurised</t>
+  </si>
+  <si>
+    <t>drain</t>
+  </si>
+  <si>
+    <t>ditch</t>
+  </si>
+  <si>
+    <t>fairway</t>
+  </si>
+  <si>
+    <t>fish_pass</t>
+  </si>
+  <si>
+    <t>canoe_pass</t>
+  </si>
+  <si>
+    <t>dam</t>
+  </si>
+  <si>
+    <t>weir</t>
+  </si>
+  <si>
+    <t>waterfall</t>
+  </si>
+  <si>
+    <t>rapids</t>
+  </si>
+  <si>
+    <t>lock_gate</t>
+  </si>
+  <si>
+    <t>sluice_gate</t>
+  </si>
+  <si>
+    <t>floodgate</t>
+  </si>
+  <si>
+    <t>debris_screen</t>
+  </si>
+  <si>
+    <t>security_lock</t>
+  </si>
+  <si>
+    <t>check_dam</t>
+  </si>
+  <si>
+    <t>turning_point</t>
+  </si>
+  <si>
+    <t>waterway</t>
+  </si>
+  <si>
+    <t>accountant</t>
+  </si>
+  <si>
+    <t>advertising_agency</t>
+  </si>
+  <si>
+    <t>airline</t>
+  </si>
+  <si>
+    <t>architect</t>
+  </si>
+  <si>
+    <t>association</t>
+  </si>
+  <si>
+    <t>broadcaster</t>
+  </si>
+  <si>
+    <t>chamber</t>
+  </si>
+  <si>
+    <t>company</t>
+  </si>
+  <si>
+    <t>construction_company</t>
+  </si>
+  <si>
+    <t>consulting</t>
+  </si>
+  <si>
+    <t>courier</t>
+  </si>
+  <si>
+    <t>coworking</t>
+  </si>
+  <si>
+    <t>diplomatic</t>
+  </si>
+  <si>
+    <t>educational_institution</t>
+  </si>
+  <si>
+    <t>employment_agency</t>
+  </si>
+  <si>
+    <t>energy_supplier</t>
+  </si>
+  <si>
+    <t>engineer</t>
+  </si>
+  <si>
+    <t>estate_agent</t>
+  </si>
+  <si>
+    <t>event_management</t>
+  </si>
+  <si>
+    <t>financial</t>
+  </si>
+  <si>
+    <t>financial_advisor</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>foundation</t>
+  </si>
+  <si>
+    <t>geodesist</t>
+  </si>
+  <si>
+    <t>gongo</t>
+  </si>
+  <si>
+    <t>government</t>
+  </si>
+  <si>
+    <t>graphic_design</t>
+  </si>
+  <si>
+    <t>guide</t>
+  </si>
+  <si>
+    <t>harbour_master</t>
+  </si>
+  <si>
+    <t>insurance</t>
+  </si>
+  <si>
+    <t>it</t>
+  </si>
+  <si>
+    <t>lawyer</t>
+  </si>
+  <si>
+    <t>logistics</t>
+  </si>
+  <si>
+    <t>moving_company</t>
+  </si>
+  <si>
+    <t>newspaper</t>
+  </si>
+  <si>
+    <t>ngo</t>
+  </si>
+  <si>
+    <t>notary</t>
+  </si>
+  <si>
+    <t>politician</t>
+  </si>
+  <si>
+    <t>political_party</t>
+  </si>
+  <si>
+    <t>property_management</t>
+  </si>
+  <si>
+    <t>publisher</t>
+  </si>
+  <si>
+    <t>quango</t>
+  </si>
+  <si>
+    <t>research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">security </t>
+  </si>
+  <si>
+    <t>surveyor</t>
+  </si>
+  <si>
+    <t>tax_advisor</t>
+  </si>
+  <si>
+    <t>teledommunication</t>
+  </si>
+  <si>
+    <t>transport</t>
+  </si>
+  <si>
+    <t>travel_agent</t>
+  </si>
+  <si>
+    <t>tutoring</t>
+  </si>
+  <si>
+    <t>union</t>
+  </si>
+  <si>
+    <t>visa</t>
+  </si>
+  <si>
+    <t>water_utility</t>
+  </si>
+  <si>
+    <t>office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water </t>
+  </si>
+  <si>
+    <t>cenote</t>
+  </si>
+  <si>
+    <t>lagoon</t>
+  </si>
+  <si>
+    <t>lake</t>
+  </si>
+  <si>
+    <t>oxbow</t>
+  </si>
+  <si>
+    <t>stream_pool</t>
+  </si>
+  <si>
+    <t>basin</t>
+  </si>
+  <si>
+    <t>harbour</t>
+  </si>
+  <si>
+    <t>lock</t>
+  </si>
+  <si>
+    <t>moat</t>
+  </si>
+  <si>
+    <t>pond</t>
+  </si>
+  <si>
+    <t>reflecting_pool</t>
+  </si>
+  <si>
+    <t>reservoir</t>
+  </si>
+  <si>
+    <t>wastewater</t>
+  </si>
+  <si>
+    <t>natural</t>
+  </si>
+  <si>
+    <t>fell</t>
+  </si>
+  <si>
+    <t>grassland</t>
+  </si>
+  <si>
+    <t>scrub</t>
+  </si>
+  <si>
+    <t>tree_stump</t>
+  </si>
+  <si>
+    <t>tundra</t>
+  </si>
+  <si>
+    <t>wood</t>
+  </si>
+  <si>
+    <t>bay</t>
+  </si>
+  <si>
+    <t>beach</t>
+  </si>
+  <si>
+    <t>blowhole</t>
+  </si>
+  <si>
+    <t>cape</t>
+  </si>
+  <si>
+    <t>coastline</t>
+  </si>
+  <si>
+    <t>crevasse</t>
+  </si>
+  <si>
+    <t>geyser</t>
+  </si>
+  <si>
+    <t>glacier</t>
+  </si>
+  <si>
+    <t>hot_spring</t>
+  </si>
+  <si>
+    <t>isthmus</t>
+  </si>
+  <si>
+    <t>mud</t>
+  </si>
+  <si>
+    <t>peninsula</t>
+  </si>
+  <si>
+    <t>reef</t>
+  </si>
+  <si>
+    <t>shingle</t>
+  </si>
+  <si>
+    <t>shoal</t>
+  </si>
+  <si>
+    <t>spring</t>
+  </si>
+  <si>
+    <t>strait</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>wetland</t>
+  </si>
+  <si>
+    <t>bare_rock</t>
+  </si>
+  <si>
+    <t>blockfield</t>
+  </si>
+  <si>
+    <t>cave_entrance</t>
+  </si>
+  <si>
+    <t>cliff</t>
+  </si>
+  <si>
+    <t>dune</t>
+  </si>
+  <si>
+    <t>earth_bank</t>
+  </si>
+  <si>
+    <t>fumarole</t>
+  </si>
+  <si>
+    <t>gorge</t>
+  </si>
+  <si>
+    <t>gully</t>
+  </si>
+  <si>
+    <t>hill</t>
+  </si>
+  <si>
+    <t>peak</t>
+  </si>
+  <si>
+    <t>ridge</t>
+  </si>
+  <si>
+    <t>rock</t>
+  </si>
+  <si>
+    <t>saddle</t>
+  </si>
+  <si>
+    <t>sand</t>
+  </si>
+  <si>
+    <t>scree</t>
+  </si>
+  <si>
+    <t>sinkhole</t>
+  </si>
+  <si>
+    <t>stone</t>
+  </si>
+  <si>
+    <t>volcano</t>
+  </si>
+  <si>
+    <t>healthcare</t>
+  </si>
+  <si>
+    <t>alternative</t>
+  </si>
+  <si>
+    <t>audiologist</t>
+  </si>
+  <si>
+    <t>birthing_centre</t>
+  </si>
+  <si>
+    <t>blood_bank</t>
+  </si>
+  <si>
+    <t>community_health_worker</t>
+  </si>
+  <si>
+    <t>counselling</t>
+  </si>
+  <si>
+    <t>dialysis</t>
+  </si>
+  <si>
+    <t>hospice</t>
+  </si>
+  <si>
+    <t>laboratory</t>
+  </si>
+  <si>
+    <t>medical_imaging</t>
+  </si>
+  <si>
+    <t>midwife</t>
+  </si>
+  <si>
+    <t>nurse</t>
+  </si>
+  <si>
+    <t>occupational_therapist</t>
+  </si>
+  <si>
+    <t>optometrist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pharmacy </t>
+  </si>
+  <si>
+    <t>physiotherapist</t>
+  </si>
+  <si>
+    <t>podiastrist</t>
+  </si>
+  <si>
+    <t>psychotherapist</t>
+  </si>
+  <si>
+    <t>rehabilitation</t>
+  </si>
+  <si>
+    <t>sample_collection</t>
+  </si>
+  <si>
+    <t>speech_therapist</t>
+  </si>
+  <si>
+    <t>vaccination_centre</t>
+  </si>
+  <si>
+    <t>postpartum_care</t>
+  </si>
+  <si>
+    <t>historic</t>
+  </si>
+  <si>
+    <t>aircraft</t>
+  </si>
+  <si>
+    <t>anchor</t>
+  </si>
+  <si>
+    <t>aqueduct</t>
+  </si>
+  <si>
+    <t>archaelogical_site</t>
+  </si>
+  <si>
+    <t>battlefield</t>
+  </si>
+  <si>
+    <t>bomb_crater</t>
+  </si>
+  <si>
+    <t>boundary_stone</t>
+  </si>
+  <si>
+    <t>building</t>
+  </si>
+  <si>
+    <t>bullaun_stone</t>
+  </si>
+  <si>
+    <t>cannon</t>
+  </si>
+  <si>
+    <t>caravanserai</t>
+  </si>
+  <si>
+    <t>castle</t>
+  </si>
+  <si>
+    <t>castle_wall</t>
+  </si>
+  <si>
+    <t>cattle_crush</t>
+  </si>
+  <si>
+    <t>charcoal_pile</t>
+  </si>
+  <si>
+    <t>church</t>
+  </si>
+  <si>
+    <t>city_gate</t>
+  </si>
+  <si>
+    <t>citywalls</t>
+  </si>
+  <si>
+    <t>creamery</t>
+  </si>
+  <si>
+    <t>district</t>
+  </si>
+  <si>
+    <t>epigraph</t>
+  </si>
+  <si>
+    <t>fort</t>
+  </si>
+  <si>
+    <t>gallows</t>
+  </si>
+  <si>
+    <t>house</t>
+  </si>
+  <si>
+    <t>high_cross</t>
+  </si>
+  <si>
+    <t>highwater_mark</t>
+  </si>
+  <si>
+    <t>lavoir</t>
+  </si>
+  <si>
+    <t>lime_kiln</t>
+  </si>
+  <si>
+    <t>locomotive</t>
+  </si>
+  <si>
+    <t>machine</t>
+  </si>
+  <si>
+    <t>manor</t>
+  </si>
+  <si>
+    <t>memorial</t>
+  </si>
+  <si>
+    <t>milestone</t>
+  </si>
+  <si>
+    <t>millstone</t>
+  </si>
+  <si>
+    <t>mine</t>
+  </si>
+  <si>
+    <t>minecart</t>
+  </si>
+  <si>
+    <t>mosque</t>
+  </si>
+  <si>
+    <t>ogham_stone</t>
+  </si>
+  <si>
+    <t>optical_telegraph</t>
+  </si>
+  <si>
+    <t>pillory</t>
+  </si>
+  <si>
+    <t>pound</t>
+  </si>
+  <si>
+    <t>railway_car</t>
+  </si>
+  <si>
+    <t>road</t>
+  </si>
+  <si>
+    <t>ruins</t>
+  </si>
+  <si>
+    <t>rune_stone</t>
+  </si>
+  <si>
+    <t>shieling</t>
+  </si>
+  <si>
+    <t>ship</t>
+  </si>
+  <si>
+    <t>stećak</t>
+  </si>
+  <si>
+    <t>tank</t>
+  </si>
+  <si>
+    <t>temple</t>
+  </si>
+  <si>
+    <t>tower</t>
+  </si>
+  <si>
+    <t>vehicle</t>
+  </si>
+  <si>
+    <t>wayside_cross</t>
+  </si>
+  <si>
+    <t>wayside_shrine</t>
+  </si>
+  <si>
+    <t>wreck</t>
+  </si>
+  <si>
+    <t>warehouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">building </t>
+  </si>
+  <si>
+    <t>apartments</t>
+  </si>
+  <si>
+    <t>barracks</t>
+  </si>
+  <si>
+    <t>bungalow</t>
+  </si>
+  <si>
+    <t>cabin</t>
+  </si>
+  <si>
+    <t>detached</t>
+  </si>
+  <si>
+    <t>annexe</t>
+  </si>
+  <si>
+    <t>dormitory</t>
+  </si>
+  <si>
+    <t>ger</t>
+  </si>
+  <si>
+    <t>houseboat</t>
+  </si>
+  <si>
+    <t>residential</t>
+  </si>
+  <si>
+    <t>semidetached-house</t>
+  </si>
+  <si>
+    <t>static_caravan</t>
+  </si>
+  <si>
+    <t>stilt_house</t>
+  </si>
+  <si>
+    <t>terrace</t>
+  </si>
+  <si>
+    <t>tree_house</t>
+  </si>
+  <si>
+    <t>trullo</t>
+  </si>
+  <si>
+    <t>commercial</t>
+  </si>
+  <si>
+    <t>industrial</t>
+  </si>
+  <si>
+    <t>retail</t>
+  </si>
+  <si>
+    <t>religious</t>
+  </si>
+  <si>
+    <t>cathedral</t>
+  </si>
+  <si>
+    <t>chapel</t>
+  </si>
+  <si>
+    <t>kingdom_hall</t>
+  </si>
+  <si>
+    <t>presbytery</t>
+  </si>
+  <si>
+    <t>shrine</t>
+  </si>
+  <si>
+    <t>synagogue</t>
+  </si>
+  <si>
+    <t>bakehouse</t>
+  </si>
+  <si>
+    <t>bridge</t>
+  </si>
+  <si>
+    <t>civic</t>
+  </si>
+  <si>
+    <t>clock_tower</t>
+  </si>
+  <si>
+    <t>gatehouse</t>
+  </si>
+  <si>
+    <t>kindergarten</t>
+  </si>
+  <si>
+    <t>public</t>
+  </si>
+  <si>
+    <t>toilets</t>
+  </si>
+  <si>
+    <t>train_station</t>
+  </si>
+  <si>
+    <t>transportation</t>
+  </si>
+  <si>
+    <t>barn</t>
+  </si>
+  <si>
+    <t>conservatory</t>
+  </si>
+  <si>
+    <t>cowshed</t>
+  </si>
+  <si>
+    <t>farm_auxiliary</t>
+  </si>
+  <si>
+    <t>greenhouse</t>
+  </si>
+  <si>
+    <t>slurry_tank</t>
+  </si>
+  <si>
+    <t>stable</t>
+  </si>
+  <si>
+    <t>sty</t>
+  </si>
+  <si>
+    <t>livestock</t>
+  </si>
+  <si>
+    <t>grandstand</t>
+  </si>
+  <si>
+    <t>pavilion</t>
+  </si>
+  <si>
+    <t>riding_hall</t>
+  </si>
+  <si>
+    <t>windmill</t>
+  </si>
+  <si>
+    <t>allotment_house</t>
+  </si>
+  <si>
+    <t>boathouse</t>
+  </si>
+  <si>
+    <t>hangar</t>
+  </si>
+  <si>
+    <t>hut</t>
+  </si>
+  <si>
+    <t>shed</t>
+  </si>
+  <si>
+    <t>carport</t>
+  </si>
+  <si>
+    <t>garage</t>
+  </si>
+  <si>
+    <t>garages</t>
+  </si>
+  <si>
+    <t>digester</t>
+  </si>
+  <si>
+    <t>service</t>
+  </si>
+  <si>
+    <t>tech_cab</t>
+  </si>
+  <si>
+    <t>transformer_tower</t>
+  </si>
+  <si>
+    <t>water_tower</t>
+  </si>
+  <si>
+    <t>storage_tank</t>
+  </si>
+  <si>
+    <t>silo</t>
+  </si>
+  <si>
+    <t>beach_hut</t>
+  </si>
+  <si>
+    <t>bunker</t>
+  </si>
+  <si>
+    <t>constructions</t>
+  </si>
+  <si>
+    <t>container</t>
+  </si>
+  <si>
+    <t>guardhouse</t>
+  </si>
+  <si>
+    <t>military</t>
+  </si>
+  <si>
+    <t>outbuilding</t>
+  </si>
+  <si>
+    <t>pagoda</t>
+  </si>
+  <si>
+    <t>quonset_hut</t>
+  </si>
+  <si>
+    <t>roof</t>
+  </si>
+  <si>
+    <t>tent</t>
+  </si>
+  <si>
+    <t>triumphal_arch</t>
+  </si>
+  <si>
+    <t>academy</t>
+  </si>
+  <si>
+    <t>airfield</t>
+  </si>
+  <si>
+    <t>base</t>
+  </si>
+  <si>
+    <t>checkpoint</t>
+  </si>
+  <si>
+    <t>danger_area</t>
+  </si>
+  <si>
+    <t>nuclear_explosion_site</t>
+  </si>
+  <si>
+    <t>obstacle_course</t>
+  </si>
+  <si>
+    <t>range</t>
+  </si>
+  <si>
+    <t>training_area</t>
+  </si>
+  <si>
+    <t>trench</t>
+  </si>
+  <si>
+    <t>sport</t>
+  </si>
+  <si>
+    <t>bowling</t>
+  </si>
+  <si>
+    <t>aerobics</t>
+  </si>
+  <si>
+    <t>american_football</t>
+  </si>
+  <si>
+    <t>aikido</t>
+  </si>
+  <si>
+    <t>archery</t>
+  </si>
+  <si>
+    <t>athletics</t>
+  </si>
+  <si>
+    <t>australian_football</t>
+  </si>
+  <si>
+    <t>badminton</t>
+  </si>
+  <si>
+    <t>bandy</t>
+  </si>
+  <si>
+    <t>baseball</t>
+  </si>
+  <si>
+    <t>basketball</t>
+  </si>
+  <si>
+    <t>beachvolleyball</t>
+  </si>
+  <si>
+    <t>biathlon</t>
+  </si>
+  <si>
+    <t>billiards</t>
+  </si>
+  <si>
+    <t>bmx</t>
+  </si>
+  <si>
+    <t>bobsleigh</t>
+  </si>
+  <si>
+    <t>boules</t>
+  </si>
+  <si>
+    <t>bowls</t>
+  </si>
+  <si>
+    <t>boxing</t>
+  </si>
+  <si>
+    <t>bullfighting</t>
+  </si>
+  <si>
+    <t>canadian_football</t>
+  </si>
+  <si>
+    <t>candlepin</t>
+  </si>
+  <si>
+    <t>canoe</t>
+  </si>
+  <si>
+    <t>chess</t>
+  </si>
+  <si>
+    <t>climbing</t>
+  </si>
+  <si>
+    <t>cockfighting</t>
+  </si>
+  <si>
+    <t>cricket</t>
+  </si>
+  <si>
+    <t>crossfit</t>
+  </si>
+  <si>
+    <t>croquet</t>
+  </si>
+  <si>
+    <t>curling</t>
+  </si>
+  <si>
+    <t>cycle_polo</t>
+  </si>
+  <si>
+    <t>cycling</t>
+  </si>
+  <si>
+    <t>darts</t>
+  </si>
+  <si>
+    <t>diving</t>
+  </si>
+  <si>
+    <t>dog_agility</t>
+  </si>
+  <si>
+    <t>dog_racing</t>
+  </si>
+  <si>
+    <t>dragon_boat</t>
+  </si>
+  <si>
+    <t>equestrian</t>
+  </si>
+  <si>
+    <t>fencing</t>
+  </si>
+  <si>
+    <t>field_hockey</t>
+  </si>
+  <si>
+    <t>fitness</t>
+  </si>
+  <si>
+    <t>five-a-side</t>
+  </si>
+  <si>
+    <t>floorball</t>
+  </si>
+  <si>
+    <t>four_square</t>
+  </si>
+  <si>
+    <t>soccer</t>
+  </si>
+  <si>
+    <t>free_flying</t>
+  </si>
+  <si>
+    <t>futnet</t>
+  </si>
+  <si>
+    <t>futsal</t>
+  </si>
+  <si>
+    <t>gaelic_games</t>
+  </si>
+  <si>
+    <t>gaga</t>
+  </si>
+  <si>
+    <t>golf</t>
+  </si>
+  <si>
+    <t>gymnastics</t>
+  </si>
+  <si>
+    <t>handball</t>
+  </si>
+  <si>
+    <t>hapkido</t>
+  </si>
+  <si>
+    <t>hiking</t>
+  </si>
+  <si>
+    <t>horseshoes</t>
+  </si>
+  <si>
+    <t>horse_racing</t>
+  </si>
+  <si>
+    <t>ice_hockey</t>
+  </si>
+  <si>
+    <t>ice_skating</t>
+  </si>
+  <si>
+    <t>ice_stock</t>
+  </si>
+  <si>
+    <t>judo</t>
+  </si>
+  <si>
+    <t>karate</t>
+  </si>
+  <si>
+    <t>karting</t>
+  </si>
+  <si>
+    <t>kickboxing</t>
+  </si>
+  <si>
+    <t>kick_scooter</t>
+  </si>
+  <si>
+    <t>kitesurfing</t>
+  </si>
+  <si>
+    <t>korfball</t>
+  </si>
+  <si>
+    <t>krachtbal</t>
+  </si>
+  <si>
+    <t>lacrosse</t>
+  </si>
+  <si>
+    <t>laser_tag</t>
+  </si>
+  <si>
+    <t>longbowl</t>
+  </si>
+  <si>
+    <t>martial_arts</t>
+  </si>
+  <si>
+    <t>model_aerodrome</t>
+  </si>
+  <si>
+    <t>motorcross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">motor </t>
+  </si>
+  <si>
+    <t>netball</t>
+  </si>
+  <si>
+    <t>nine_mens_morris</t>
+  </si>
+  <si>
+    <t>orienteering</t>
+  </si>
+  <si>
+    <t>paddle_tennis</t>
+  </si>
+  <si>
+    <t>padel</t>
+  </si>
+  <si>
+    <t>paintball</t>
+  </si>
+  <si>
+    <t>parachuting</t>
+  </si>
+  <si>
+    <t>parkour</t>
+  </si>
+  <si>
+    <t>pelota</t>
+  </si>
+  <si>
+    <t>pesäpallo</t>
+  </si>
+  <si>
+    <t>pickleball</t>
+  </si>
+  <si>
+    <t>pilates</t>
+  </si>
+  <si>
+    <t>pole_dance</t>
+  </si>
+  <si>
+    <t>powerlifting</t>
+  </si>
+  <si>
+    <t>racquet</t>
+  </si>
+  <si>
+    <t>rc_car</t>
+  </si>
+  <si>
+    <t>roller_skating</t>
+  </si>
+  <si>
+    <t>rowing</t>
+  </si>
+  <si>
+    <t>rugby_league</t>
+  </si>
+  <si>
+    <t>rugby_union</t>
+  </si>
+  <si>
+    <t>running</t>
+  </si>
+  <si>
+    <t>sailing</t>
+  </si>
+  <si>
+    <t>seatball</t>
+  </si>
+  <si>
+    <t>shooting</t>
+  </si>
+  <si>
+    <t>shot-put</t>
+  </si>
+  <si>
+    <t>skateboard</t>
+  </si>
+  <si>
+    <t>ski_jumping</t>
+  </si>
+  <si>
+    <t>skiing</t>
+  </si>
+  <si>
+    <t>snooker</t>
+  </si>
+  <si>
+    <t>softball</t>
+  </si>
+  <si>
+    <t>speedway</t>
+  </si>
+  <si>
+    <t>squash</t>
+  </si>
+  <si>
+    <t>sumo</t>
+  </si>
+  <si>
+    <t>surfing</t>
+  </si>
+  <si>
+    <t>swimming</t>
+  </si>
+  <si>
+    <t>table_tennis</t>
+  </si>
+  <si>
+    <t>table_soccer</t>
+  </si>
+  <si>
+    <t>taekwondo</t>
+  </si>
+  <si>
+    <t>tennis</t>
+  </si>
+  <si>
+    <t>teqball</t>
+  </si>
+  <si>
+    <t>toboggan</t>
+  </si>
+  <si>
+    <t>ultimate</t>
+  </si>
+  <si>
+    <t>ultralight_aviation</t>
+  </si>
+  <si>
+    <t>volleyball</t>
+  </si>
+  <si>
+    <t>wakeboarding</t>
+  </si>
+  <si>
+    <t>water_polo</t>
+  </si>
+  <si>
+    <t>water_ski</t>
+  </si>
+  <si>
+    <t>weightlifting</t>
+  </si>
+  <si>
+    <t>windsurfing</t>
+  </si>
+  <si>
+    <t>wrestling</t>
+  </si>
+  <si>
+    <t>yoga</t>
+  </si>
+  <si>
+    <t>Q3177899</t>
+  </si>
+  <si>
+    <t>Q215641</t>
+  </si>
+  <si>
+    <t>Q41323</t>
+  </si>
+  <si>
+    <t>Q43114</t>
+  </si>
+  <si>
+    <t>Q108429</t>
+  </si>
+  <si>
+    <t>Q542</t>
+  </si>
+  <si>
+    <t>Q50776</t>
+  </si>
+  <si>
+    <t>Q7291</t>
+  </si>
+  <si>
+    <t>Q183018</t>
+  </si>
+  <si>
+    <t>Q809831</t>
+  </si>
+  <si>
+    <t>Q5369</t>
+  </si>
+  <si>
+    <t>Q5372</t>
+  </si>
+  <si>
+    <t>Q4543</t>
+  </si>
+  <si>
+    <t>Q166788</t>
+  </si>
+  <si>
+    <t>Q3341285</t>
+  </si>
+  <si>
+    <t>Q215184</t>
+  </si>
+  <si>
+    <t>Q177275</t>
+  </si>
+  <si>
+    <t>Q895060</t>
+  </si>
+  <si>
+    <t>Q895471</t>
+  </si>
+  <si>
+    <t>Q32112</t>
+  </si>
+  <si>
+    <t>Q184940</t>
+  </si>
+  <si>
+    <t>Q248534</t>
+  </si>
+  <si>
+    <t>Q5031973</t>
+  </si>
+  <si>
+    <t>Q171529</t>
+  </si>
+  <si>
+    <t>Q718</t>
+  </si>
+  <si>
+    <t>Q5132811</t>
+  </si>
+  <si>
+    <t>cliff_diving</t>
+  </si>
+  <si>
+    <t>Q22857</t>
+  </si>
+  <si>
+    <t>climbing_adventure</t>
+  </si>
+  <si>
+    <t>Q319771</t>
+  </si>
+  <si>
+    <t>Q5375</t>
+  </si>
+  <si>
+    <t>Q2072840</t>
+  </si>
+  <si>
+    <t>Q136851</t>
+  </si>
+  <si>
+    <t>Q193387</t>
+  </si>
+  <si>
+    <t>Q429885</t>
+  </si>
+  <si>
+    <t>Q2215841</t>
+  </si>
+  <si>
+    <t>Q11639</t>
+  </si>
+  <si>
+    <t>Q131471</t>
+  </si>
+  <si>
+    <t>Q7735</t>
+  </si>
+  <si>
+    <t>Q393808</t>
+  </si>
+  <si>
+    <t>Q57833661</t>
+  </si>
+  <si>
+    <t>Q57589</t>
+  </si>
+  <si>
+    <t>Q902378</t>
+  </si>
+  <si>
+    <t>Q12100</t>
+  </si>
+  <si>
+    <t>Q1455</t>
+  </si>
+  <si>
+    <t>Q219067</t>
+  </si>
+  <si>
+    <t>Q2250158</t>
+  </si>
+  <si>
+    <t>Q206763</t>
+  </si>
+  <si>
+    <t>Q1439993</t>
+  </si>
+  <si>
+    <t>Q2736</t>
+  </si>
+  <si>
+    <t>Q855880</t>
+  </si>
+  <si>
+    <t>Q171401</t>
+  </si>
+  <si>
+    <t>Q2447366</t>
+  </si>
+  <si>
+    <t>Q5377</t>
+  </si>
+  <si>
+    <t>Q43450</t>
+  </si>
+  <si>
+    <t>Q8418</t>
+  </si>
+  <si>
+    <t>Q200333</t>
+  </si>
+  <si>
+    <t>Q12014035</t>
+  </si>
+  <si>
+    <t>Q2746282</t>
+  </si>
+  <si>
+    <t>Q187916</t>
+  </si>
+  <si>
+    <t>Q41466</t>
+  </si>
+  <si>
+    <t>Q779272</t>
+  </si>
+  <si>
+    <t>Q1070325</t>
+  </si>
+  <si>
+    <t>Q11420</t>
+  </si>
+  <si>
+    <t>Q11419</t>
+  </si>
+  <si>
+    <t>Q192420</t>
+  </si>
+  <si>
+    <t>Q178678</t>
+  </si>
+  <si>
+    <t>Q502057</t>
+  </si>
+  <si>
+    <t>Q219554</t>
+  </si>
+  <si>
+    <t>Q192937</t>
+  </si>
+  <si>
+    <t>Q2280583</t>
+  </si>
+  <si>
+    <t>Q185851</t>
+  </si>
+  <si>
+    <t>Q998303</t>
+  </si>
+  <si>
+    <t>Q11417</t>
+  </si>
+  <si>
+    <t>Q2475583</t>
+  </si>
+  <si>
+    <t>Q215862</t>
+  </si>
+  <si>
+    <t>Q5367</t>
+  </si>
+  <si>
+    <t>Q231200</t>
+  </si>
+  <si>
+    <t>Q209669</t>
+  </si>
+  <si>
+    <t>Q4703797</t>
+  </si>
+  <si>
+    <t>Q29358</t>
+  </si>
+  <si>
+    <t>Q1582389</t>
+  </si>
+  <si>
+    <t>Q192832</t>
+  </si>
+  <si>
+    <t>Q193210</t>
+  </si>
+  <si>
+    <t>Q483693</t>
+  </si>
+  <si>
+    <t>Q11928176</t>
+  </si>
+  <si>
+    <t>Q1295867</t>
+  </si>
+  <si>
+    <t>Q866224</t>
+  </si>
+  <si>
+    <t>Q272460</t>
+  </si>
+  <si>
+    <t>Q218998</t>
+  </si>
+  <si>
+    <t>Q213796</t>
+  </si>
+  <si>
+    <t>Q754586</t>
+  </si>
+  <si>
+    <t>Q1419833</t>
+  </si>
+  <si>
+    <t>Q1707432</t>
+  </si>
+  <si>
+    <t>Q159354</t>
+  </si>
+  <si>
+    <t>Q10962</t>
+  </si>
+  <si>
+    <t>Q5849</t>
+  </si>
+  <si>
+    <t>Q105674</t>
+  </si>
+  <si>
+    <t>Q14085739</t>
+  </si>
+  <si>
+    <t>Q1096878</t>
+  </si>
+  <si>
+    <t>Q2290709</t>
+  </si>
+  <si>
+    <t>Q2252077</t>
+  </si>
+  <si>
+    <t>Q180935</t>
+  </si>
+  <si>
+    <t>Q842284</t>
+  </si>
+  <si>
+    <t>Q7718</t>
+  </si>
+  <si>
+    <t>Q130949</t>
+  </si>
+  <si>
+    <t>Q11015</t>
+  </si>
+  <si>
+    <t>Q171038</t>
+  </si>
+  <si>
+    <t>Q750080</t>
+  </si>
+  <si>
+    <t>Q133201</t>
+  </si>
+  <si>
+    <t>Q40561</t>
+  </si>
+  <si>
+    <t>Q159992</t>
+  </si>
+  <si>
+    <t>Q31920</t>
+  </si>
+  <si>
+    <t>Q3930</t>
+  </si>
+  <si>
+    <t>Q14922</t>
+  </si>
+  <si>
+    <t>Q36389</t>
+  </si>
+  <si>
+    <t>Q847</t>
+  </si>
+  <si>
+    <t>Q19578052</t>
+  </si>
+  <si>
+    <t>Q135959648</t>
+  </si>
+  <si>
+    <t>trampoline</t>
+  </si>
+  <si>
+    <t>Q465014</t>
+  </si>
+  <si>
+    <t>Q244700</t>
+  </si>
+  <si>
+    <t>Q678305</t>
+  </si>
+  <si>
+    <t>Q1734</t>
+  </si>
+  <si>
+    <t>Q376040</t>
+  </si>
+  <si>
+    <t>Q7707</t>
+  </si>
+  <si>
+    <t>Q472827</t>
+  </si>
+  <si>
+    <t>Q83462</t>
+  </si>
+  <si>
+    <t>Q191051</t>
+  </si>
+  <si>
+    <t>Q42486</t>
+  </si>
+  <si>
+    <t>Q9350</t>
+  </si>
+  <si>
+    <t>Q917182</t>
+  </si>
+  <si>
+    <t>Q695850</t>
+  </si>
+  <si>
+    <t>Q245016</t>
+  </si>
+  <si>
+    <t>Q91122</t>
+  </si>
+  <si>
+    <t>Q131263</t>
+  </si>
+  <si>
+    <t>Q1783352</t>
+  </si>
+  <si>
+    <t>Q96194277</t>
+  </si>
+  <si>
+    <t>Q933851</t>
+  </si>
+  <si>
+    <t>Q136562970</t>
+  </si>
+  <si>
+    <t>Q91764</t>
+  </si>
+  <si>
+    <t>Q1778846</t>
+  </si>
+  <si>
+    <t>Q1935049</t>
+  </si>
+  <si>
+    <t>Q4022</t>
+  </si>
+  <si>
+    <t>Q47521</t>
+  </si>
+  <si>
+    <t>Q27250</t>
+  </si>
+  <si>
+    <t>Q12284</t>
+  </si>
+  <si>
+    <t>Q2048319</t>
+  </si>
+  <si>
+    <t>Q12366145</t>
+  </si>
+  <si>
+    <t>Q49110921</t>
+  </si>
+  <si>
+    <t>Q12323</t>
+  </si>
+  <si>
+    <t>Q1066997</t>
+  </si>
+  <si>
+    <t>Q34038</t>
+  </si>
+  <si>
+    <t>Q695793</t>
+  </si>
+  <si>
+    <t>Q2345125</t>
+  </si>
+  <si>
+    <t>Q4546997</t>
+  </si>
+  <si>
+    <t>Q7835737</t>
+  </si>
+  <si>
+    <t>Q24853940</t>
+  </si>
+  <si>
+    <t>Q1052083</t>
+  </si>
+  <si>
+    <t>Q1940488</t>
+  </si>
+  <si>
+    <t>Q5459912</t>
+  </si>
+  <si>
+    <t>Q850107</t>
+  </si>
+  <si>
+    <t>Q695207</t>
+  </si>
+  <si>
+    <t>Q1307276</t>
+  </si>
+  <si>
+    <t>Q3044808)</t>
+  </si>
+  <si>
+    <t>Q847950</t>
+  </si>
+  <si>
+    <t>Q131596</t>
+  </si>
+  <si>
+    <t>Q15680</t>
+  </si>
+  <si>
+    <t>Q3947</t>
+  </si>
+  <si>
+    <t>Q1321309</t>
+  </si>
+  <si>
+    <t>Q11755880</t>
+  </si>
+  <si>
+    <t>Q113575165</t>
+  </si>
+  <si>
+    <t>(Q1434998</t>
+  </si>
+  <si>
+    <t>Q33565</t>
+  </si>
+  <si>
+    <t>Q641406</t>
+  </si>
+  <si>
+    <t>Q5784194</t>
+  </si>
+  <si>
+    <t>Q323069</t>
+  </si>
+  <si>
+    <t>Q655686</t>
+  </si>
+  <si>
+    <t>Q1662011</t>
+  </si>
+  <si>
+    <t>Q1021645</t>
+  </si>
+  <si>
+    <t>Q18760388</t>
+  </si>
+  <si>
+    <t>Q181623</t>
+  </si>
+  <si>
+    <t>Q24398318</t>
+  </si>
+  <si>
+    <t>Q2977</t>
+  </si>
+  <si>
+    <t>Q108325</t>
+  </si>
+  <si>
+    <t>Q16970</t>
+  </si>
+  <si>
+    <t>Q743165</t>
+  </si>
+  <si>
+    <t>Q32815</t>
+  </si>
+  <si>
+    <t>Q607241</t>
+  </si>
+  <si>
+    <t>Q697295</t>
+  </si>
+  <si>
+    <t>Q34627</t>
+  </si>
+  <si>
+    <t>Q44539</t>
+  </si>
+  <si>
+    <t>Q798436</t>
+  </si>
+  <si>
+    <t>Q12280</t>
+  </si>
+  <si>
+    <t>Q52177058</t>
+  </si>
+  <si>
+    <t>Q853854</t>
+  </si>
+  <si>
+    <t>Q16831714</t>
+  </si>
+  <si>
+    <t>Q277760</t>
+  </si>
+  <si>
+    <t>Q24699794</t>
+  </si>
+  <si>
+    <t>Q39364723</t>
+  </si>
+  <si>
+    <t>Q294422</t>
+  </si>
+  <si>
+    <t>Q1244442</t>
+  </si>
+  <si>
+    <t>Q126127572</t>
+  </si>
+  <si>
+    <t>Q1339195</t>
+  </si>
+  <si>
+    <t>Q2516121</t>
+  </si>
+  <si>
+    <t>Q19844914</t>
+  </si>
+  <si>
+    <t>Q1303167</t>
+  </si>
+  <si>
+    <t>Q20077174</t>
+  </si>
+  <si>
+    <t>Q681337</t>
+  </si>
+  <si>
+    <t>Q10480682</t>
+  </si>
+  <si>
+    <t>Q165044</t>
+  </si>
+  <si>
+    <t>Q1560125</t>
+  </si>
+  <si>
+    <t>Q214252</t>
+  </si>
+  <si>
+    <t>Q1651566</t>
+  </si>
+  <si>
+    <t>Q1796966</t>
+  </si>
+  <si>
+    <t>Q276173</t>
+  </si>
+  <si>
+    <t>Q3503155</t>
+  </si>
+  <si>
+    <t>Q38720</t>
+  </si>
+  <si>
+    <t>Q47525299</t>
+  </si>
+  <si>
+    <t>Q1777951</t>
+  </si>
+  <si>
+    <t>Q192375</t>
+  </si>
+  <si>
+    <t>Q5784097</t>
+  </si>
+  <si>
+    <t>Q721931</t>
+  </si>
+  <si>
+    <t>Q1044817</t>
+  </si>
+  <si>
+    <t>Q22733</t>
+  </si>
+  <si>
+    <t>Q13218805</t>
+  </si>
+  <si>
+    <t>Q289633</t>
+  </si>
+  <si>
+    <t>Q1912748</t>
+  </si>
+  <si>
+    <t>Q2461128</t>
+  </si>
+  <si>
+    <t>Q274153</t>
+  </si>
+  <si>
+    <t>Q1047832</t>
+  </si>
+  <si>
+    <t>Q213643</t>
+  </si>
+  <si>
+    <t>Q2286379</t>
+  </si>
+  <si>
+    <t>Q23413</t>
+  </si>
+  <si>
+    <t>Q12377751</t>
+  </si>
+  <si>
+    <t>Q1128503</t>
+  </si>
+  <si>
+    <t>Q2914427</t>
+  </si>
+  <si>
+    <t>Q6852233</t>
+  </si>
+  <si>
+    <t>Q3044808</t>
+  </si>
+  <si>
+    <t>Q199451</t>
+  </si>
+  <si>
+    <t>Q1627026</t>
+  </si>
+  <si>
+    <t>Q83180</t>
+  </si>
+  <si>
+    <t>Q109607</t>
+  </si>
+  <si>
+    <t>Q12518</t>
+  </si>
+  <si>
+    <t>Q143912</t>
+  </si>
+  <si>
+    <t>Q326653</t>
+  </si>
+  <si>
+    <t>Q216931</t>
+  </si>
+  <si>
+    <t>Q46970</t>
+  </si>
+  <si>
+    <t>Q42973</t>
+  </si>
+  <si>
+    <t>Q15911314</t>
+  </si>
+  <si>
+    <t>Q141683</t>
+  </si>
+  <si>
+    <t>Q708676</t>
+  </si>
+  <si>
+    <t>Q6881511</t>
+  </si>
+  <si>
+    <t>Q811930</t>
+  </si>
+  <si>
+    <t>Q63769412</t>
+  </si>
+  <si>
+    <t>Q848466</t>
+  </si>
+  <si>
+    <t>Q5341295</t>
+  </si>
+  <si>
+    <t>Q261362</t>
+  </si>
+  <si>
+    <t>Q26897700</t>
+  </si>
+  <si>
+    <t>Q81096</t>
+  </si>
+  <si>
+    <t>Q1660104</t>
+  </si>
+  <si>
+    <t>Q1381931</t>
+  </si>
+  <si>
+    <t>Q683476</t>
+  </si>
+  <si>
+    <t>Q38112</t>
+  </si>
+  <si>
+    <t>Q157031</t>
+  </si>
+  <si>
+    <t>Q116994205</t>
+  </si>
+  <si>
+    <t>Q2082226</t>
+  </si>
+  <si>
+    <t>Q7188</t>
+  </si>
+  <si>
+    <t>Q185925</t>
+  </si>
+  <si>
+    <t>Q2073907</t>
+  </si>
+  <si>
+    <t>Q1489454</t>
+  </si>
+  <si>
+    <t>Q11661</t>
+  </si>
+  <si>
+    <t>Q43183</t>
+  </si>
+  <si>
+    <t>Q177777</t>
+  </si>
+  <si>
+    <t>Q1757263</t>
+  </si>
+  <si>
+    <t>Q40348</t>
+  </si>
+  <si>
+    <t>Q11032</t>
+  </si>
+  <si>
+    <t>Q79913</t>
+  </si>
+  <si>
+    <t>Q189010</t>
+  </si>
+  <si>
+    <t>Q82955</t>
+  </si>
+  <si>
+    <t>Q7278</t>
+  </si>
+  <si>
+    <t>Q1618728</t>
+  </si>
+  <si>
+    <t>Q2085381</t>
+  </si>
+  <si>
+    <t>Q1940786</t>
+  </si>
+  <si>
+    <t>Q19829980</t>
+  </si>
+  <si>
+    <t>Q42240</t>
+  </si>
+  <si>
+    <t>Q137651948</t>
+  </si>
+  <si>
+    <t>Q294126</t>
+  </si>
+  <si>
+    <t>Q688576</t>
+  </si>
+  <si>
+    <t>Q2401749</t>
+  </si>
+  <si>
+    <t>Q740752</t>
+  </si>
+  <si>
+    <t>Q2141946</t>
+  </si>
+  <si>
+    <t>Q901222</t>
+  </si>
+  <si>
+    <t>Q178790</t>
+  </si>
+  <si>
+    <t>Q7258040</t>
+  </si>
+  <si>
+    <t>Q112726458</t>
+  </si>
+  <si>
+    <t>Q334743</t>
+  </si>
+  <si>
+    <t>Q187223</t>
+  </si>
+  <si>
+    <t>Q23397</t>
+  </si>
+  <si>
+    <t>Q209333</t>
+  </si>
+  <si>
+    <t>Q2385513</t>
+  </si>
+  <si>
+    <t>Q813672</t>
+  </si>
+  <si>
+    <t>Q105731</t>
+  </si>
+  <si>
+    <t>Q88480</t>
+  </si>
+  <si>
+    <t>Q3253281</t>
+  </si>
+  <si>
+    <t>Q131681</t>
+  </si>
+  <si>
+    <t>Q1328914</t>
+  </si>
+  <si>
+    <t>Q15242449</t>
+  </si>
+  <si>
+    <t>Q5421955</t>
+  </si>
+  <si>
+    <t>Q1006733</t>
+  </si>
+  <si>
+    <t>heath</t>
+  </si>
+  <si>
+    <t>Q27590</t>
+  </si>
+  <si>
+    <t>Q879641</t>
+  </si>
+  <si>
+    <t>Q811646</t>
+  </si>
+  <si>
+    <t>Q43262</t>
+  </si>
+  <si>
+    <t>Q4421</t>
+  </si>
+  <si>
+    <t>Q39594</t>
+  </si>
+  <si>
+    <t>Q40080</t>
+  </si>
+  <si>
+    <t>Q389545</t>
+  </si>
+  <si>
+    <t>Q185113</t>
+  </si>
+  <si>
+    <t>Q1701967</t>
+  </si>
+  <si>
+    <t>Q862193</t>
+  </si>
+  <si>
+    <t>Q83471</t>
+  </si>
+  <si>
+    <t>Q35666</t>
+  </si>
+  <si>
+    <t>Q177380</t>
+  </si>
+  <si>
+    <t>Q93267</t>
+  </si>
+  <si>
+    <t>Q170449</t>
+  </si>
+  <si>
+    <t>Q34763</t>
+  </si>
+  <si>
+    <t>Q184358</t>
+  </si>
+  <si>
+    <t>Q28337</t>
+  </si>
+  <si>
+    <t>Q1059407</t>
+  </si>
+  <si>
+    <t>Q124714</t>
+  </si>
+  <si>
+    <t>Q37901</t>
+  </si>
+  <si>
+    <t>Q283</t>
+  </si>
+  <si>
+    <t>Q170321</t>
+  </si>
+  <si>
+    <t>arete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arch </t>
+  </si>
+  <si>
+    <t>Q954501</t>
+  </si>
+  <si>
+    <t>Q1334383</t>
+  </si>
+  <si>
+    <t>Q570309</t>
+  </si>
+  <si>
+    <t>Q1709247</t>
+  </si>
+  <si>
+    <t>Q67166646</t>
+  </si>
+  <si>
+    <t>Q107679</t>
+  </si>
+  <si>
+    <t>Q105880</t>
+  </si>
+  <si>
+    <t>Q25391</t>
+  </si>
+  <si>
+    <t>Q150784</t>
+  </si>
+  <si>
+    <t>Q1361400</t>
+  </si>
+  <si>
+    <t>Q54050</t>
+  </si>
+  <si>
+    <t>Q207326</t>
+  </si>
+  <si>
+    <t>Q740445</t>
+  </si>
+  <si>
+    <t>Q8063</t>
+  </si>
+  <si>
+    <t>Q10862618</t>
+  </si>
+  <si>
+    <t>Q34679</t>
+  </si>
+  <si>
+    <t>Q1133195</t>
+  </si>
+  <si>
+    <t>Q188734</t>
+  </si>
+  <si>
+    <t>Q22731</t>
+  </si>
+  <si>
+    <t>Q188504</t>
+  </si>
+  <si>
+    <t>Q8072</t>
+  </si>
+  <si>
+    <t>Q1644347</t>
+  </si>
+  <si>
+    <t>Q1752787</t>
+  </si>
+  <si>
+    <t>Q763244</t>
+  </si>
+  <si>
+    <t>Q35112127</t>
+  </si>
+  <si>
+    <t>Q1004210</t>
+  </si>
+  <si>
+    <t>Q136696367</t>
+  </si>
+  <si>
+    <t>Q4895508</t>
+  </si>
+  <si>
+    <t>Q839954</t>
+  </si>
+  <si>
+    <t>Q474</t>
+  </si>
+  <si>
+    <t>Q921099</t>
+  </si>
+  <si>
+    <t>Q81103</t>
+  </si>
+  <si>
+    <t>Q186347</t>
+  </si>
+  <si>
+    <t>Q3051195</t>
+  </si>
+  <si>
+    <t>Q55374005</t>
+  </si>
+  <si>
+    <t>Q82117</t>
+  </si>
+  <si>
+    <t>Q16748868</t>
+  </si>
+  <si>
+    <t>Q61140231</t>
+  </si>
+  <si>
+    <t>Q15243209</t>
+  </si>
+  <si>
+    <t>Q1640824</t>
+  </si>
+  <si>
+    <t>Q1785071</t>
+  </si>
+  <si>
+    <t>Q243778</t>
+  </si>
+  <si>
+    <t>Q5773747</t>
+  </si>
+  <si>
+    <t>Q939644</t>
+  </si>
+  <si>
+    <t>Q1622444</t>
+  </si>
+  <si>
+    <t>Q1690211</t>
+  </si>
+  <si>
+    <t>Q59772</t>
+  </si>
+  <si>
+    <t>Q29996089</t>
+  </si>
+  <si>
+    <t>Q879050</t>
+  </si>
+  <si>
+    <t>Q5003624</t>
+  </si>
+  <si>
+    <t>Q10145</t>
+  </si>
+  <si>
+    <t>Q670985</t>
+  </si>
+  <si>
+    <t>Q820477</t>
+  </si>
+  <si>
+    <t>Q1570882</t>
+  </si>
+  <si>
+    <t>monument</t>
+  </si>
+  <si>
+    <t>Q4989906</t>
+  </si>
+  <si>
+    <t>Q2016147</t>
+  </si>
+  <si>
+    <t>Q378499</t>
+  </si>
+  <si>
+    <t>Q241212</t>
+  </si>
+  <si>
+    <t>Q4764963</t>
+  </si>
+  <si>
+    <t>Q753779</t>
+  </si>
+  <si>
+    <t>Q445741</t>
+  </si>
+  <si>
+    <t>round_tower</t>
+  </si>
+  <si>
+    <t>Q1335799</t>
+  </si>
+  <si>
+    <t>Q815241</t>
+  </si>
+  <si>
+    <t>Q76212808</t>
+  </si>
+  <si>
+    <t>Q575727</t>
+  </si>
+  <si>
+    <t>Q63724</t>
+  </si>
+  <si>
+    <t>Q2309609</t>
+  </si>
+  <si>
+    <t>Q3395121</t>
+  </si>
+  <si>
+    <t>Q852190</t>
+  </si>
+  <si>
+    <t>Q4390239</t>
+  </si>
+  <si>
+    <t>Q27349</t>
+  </si>
+  <si>
+    <t>Q391744</t>
+  </si>
+  <si>
+    <t>Q39631</t>
+  </si>
+  <si>
+    <t>Q608152</t>
+  </si>
+  <si>
+    <t>Q5154968</t>
+  </si>
+  <si>
+    <t>Q483242</t>
+  </si>
+  <si>
+    <t>Q931309</t>
+  </si>
+  <si>
+    <t>Q185196</t>
+  </si>
+  <si>
+    <t>Q186360</t>
+  </si>
+  <si>
+    <t>Q631193</t>
+  </si>
+  <si>
+    <t>Q3354501</t>
+  </si>
+  <si>
+    <t>Q614304</t>
+  </si>
+  <si>
+    <t>Q694748</t>
+  </si>
+  <si>
+    <t>Q3393065</t>
+  </si>
+  <si>
+    <t>Q1900167</t>
+  </si>
+  <si>
+    <t>Q2795791</t>
+  </si>
+  <si>
+    <t>Q104595226</t>
+  </si>
+  <si>
+    <t>Q11762416</t>
+  </si>
+  <si>
+    <t>Q104537043</t>
+  </si>
+  <si>
+    <t>Q106088007</t>
+  </si>
+  <si>
+    <t>Q56879453</t>
+  </si>
+  <si>
+    <t>Q168432</t>
+  </si>
+  <si>
+    <t>Q1865205</t>
+  </si>
+  <si>
+    <t>Q373609</t>
+  </si>
+  <si>
+    <t>Q1138251</t>
+  </si>
+  <si>
+    <t>Q11019</t>
+  </si>
+  <si>
+    <t>Q12876</t>
+  </si>
+  <si>
+    <t>Q42889</t>
+  </si>
+  <si>
+    <t>Q170544</t>
+  </si>
+  <si>
+    <t>Q178380</t>
+  </si>
+  <si>
+    <t>Q2909925</t>
+  </si>
+  <si>
+    <t>Q329294</t>
+  </si>
+  <si>
+    <t>Q97095925</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1762,6 +4384,18 @@
       <color rgb="FF54595D"/>
       <name val="Georgia"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="6.6"/>
+      <color rgb="FF54595D"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1784,12 +4418,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1805,10 +4442,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2128,10 +4761,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2645F77-54E4-4B19-94FC-FC73E6D10C88}">
-  <dimension ref="A1:C295"/>
+  <dimension ref="A1:C781"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5379,7 +8013,5355 @@
         <v>552</v>
       </c>
     </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>590</v>
+      </c>
+      <c r="B296" t="s">
+        <v>568</v>
+      </c>
+      <c r="C296" s="3" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>590</v>
+      </c>
+      <c r="B297" t="s">
+        <v>569</v>
+      </c>
+      <c r="C297" s="3" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>590</v>
+      </c>
+      <c r="B298" t="s">
+        <v>570</v>
+      </c>
+      <c r="C298" s="3" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>590</v>
+      </c>
+      <c r="B299" t="s">
+        <v>571</v>
+      </c>
+      <c r="C299" s="3" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>590</v>
+      </c>
+      <c r="B300" t="s">
+        <v>572</v>
+      </c>
+      <c r="C300" s="3" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>590</v>
+      </c>
+      <c r="B301" t="s">
+        <v>573</v>
+      </c>
+      <c r="C301" s="3" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>590</v>
+      </c>
+      <c r="B302" t="s">
+        <v>574</v>
+      </c>
+      <c r="C302" s="3" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>590</v>
+      </c>
+      <c r="B303" t="s">
+        <v>575</v>
+      </c>
+      <c r="C303" s="3" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>590</v>
+      </c>
+      <c r="B304" t="s">
+        <v>576</v>
+      </c>
+      <c r="C304" s="3" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>590</v>
+      </c>
+      <c r="B305" t="s">
+        <v>577</v>
+      </c>
+      <c r="C305" s="3" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>590</v>
+      </c>
+      <c r="B306" t="s">
+        <v>578</v>
+      </c>
+      <c r="C306" s="3" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>590</v>
+      </c>
+      <c r="B307" t="s">
+        <v>579</v>
+      </c>
+      <c r="C307" s="3" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>590</v>
+      </c>
+      <c r="B308" t="s">
+        <v>580</v>
+      </c>
+      <c r="C308" s="3" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>590</v>
+      </c>
+      <c r="B309" t="s">
+        <v>581</v>
+      </c>
+      <c r="C309" s="3" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>590</v>
+      </c>
+      <c r="B310" t="s">
+        <v>582</v>
+      </c>
+      <c r="C310" s="3" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>590</v>
+      </c>
+      <c r="B311" t="s">
+        <v>583</v>
+      </c>
+      <c r="C311" s="3" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>590</v>
+      </c>
+      <c r="B312" t="s">
+        <v>584</v>
+      </c>
+      <c r="C312" s="3" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>590</v>
+      </c>
+      <c r="B313" t="s">
+        <v>585</v>
+      </c>
+      <c r="C313" s="3" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>590</v>
+      </c>
+      <c r="B314" t="s">
+        <v>586</v>
+      </c>
+      <c r="C314" s="3" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>590</v>
+      </c>
+      <c r="B315" t="s">
+        <v>587</v>
+      </c>
+      <c r="C315" s="3" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>590</v>
+      </c>
+      <c r="B316" t="s">
+        <v>588</v>
+      </c>
+      <c r="C316" s="3" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>590</v>
+      </c>
+      <c r="B317" t="s">
+        <v>589</v>
+      </c>
+      <c r="C317" s="3" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>590</v>
+      </c>
+      <c r="B318" t="s">
+        <v>164</v>
+      </c>
+      <c r="C318" s="3" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>644</v>
+      </c>
+      <c r="B319" t="s">
+        <v>591</v>
+      </c>
+      <c r="C319" s="3" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>644</v>
+      </c>
+      <c r="B320" t="s">
+        <v>592</v>
+      </c>
+      <c r="C320" s="3" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>644</v>
+      </c>
+      <c r="B321" t="s">
+        <v>593</v>
+      </c>
+      <c r="C321" s="3" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>644</v>
+      </c>
+      <c r="B322" t="s">
+        <v>594</v>
+      </c>
+      <c r="C322" s="3" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>644</v>
+      </c>
+      <c r="B323" t="s">
+        <v>595</v>
+      </c>
+      <c r="C323" s="3" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>644</v>
+      </c>
+      <c r="B324" t="s">
+        <v>596</v>
+      </c>
+      <c r="C324" s="3" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>644</v>
+      </c>
+      <c r="B325" t="s">
+        <v>597</v>
+      </c>
+      <c r="C325" s="3" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>644</v>
+      </c>
+      <c r="B326" t="s">
+        <v>349</v>
+      </c>
+      <c r="C326" s="3" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>644</v>
+      </c>
+      <c r="B327" t="s">
+        <v>598</v>
+      </c>
+      <c r="C327" s="3" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>644</v>
+      </c>
+      <c r="B328" t="s">
+        <v>599</v>
+      </c>
+      <c r="C328" s="3" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>644</v>
+      </c>
+      <c r="B329" t="s">
+        <v>600</v>
+      </c>
+      <c r="C329" s="3" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>644</v>
+      </c>
+      <c r="B330" t="s">
+        <v>601</v>
+      </c>
+      <c r="C330" s="3" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>644</v>
+      </c>
+      <c r="B331" t="s">
+        <v>602</v>
+      </c>
+      <c r="C331" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>644</v>
+      </c>
+      <c r="B332" t="s">
+        <v>603</v>
+      </c>
+      <c r="C332" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>644</v>
+      </c>
+      <c r="B333" t="s">
+        <v>604</v>
+      </c>
+      <c r="C333" s="3" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>644</v>
+      </c>
+      <c r="B334" t="s">
+        <v>605</v>
+      </c>
+      <c r="C334" s="3" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>644</v>
+      </c>
+      <c r="B335" t="s">
+        <v>606</v>
+      </c>
+      <c r="C335" s="3" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>644</v>
+      </c>
+      <c r="B336" t="s">
+        <v>607</v>
+      </c>
+      <c r="C336" s="3" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>644</v>
+      </c>
+      <c r="B337" t="s">
+        <v>608</v>
+      </c>
+      <c r="C337" s="3" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>644</v>
+      </c>
+      <c r="B338" t="s">
+        <v>609</v>
+      </c>
+      <c r="C338" s="3" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>644</v>
+      </c>
+      <c r="B339" t="s">
+        <v>610</v>
+      </c>
+      <c r="C339" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>644</v>
+      </c>
+      <c r="B340" t="s">
+        <v>611</v>
+      </c>
+      <c r="C340" s="3" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>644</v>
+      </c>
+      <c r="B341" t="s">
+        <v>612</v>
+      </c>
+      <c r="C341" s="3" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>644</v>
+      </c>
+      <c r="B342" t="s">
+        <v>613</v>
+      </c>
+      <c r="C342" s="3" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>644</v>
+      </c>
+      <c r="B343" t="s">
+        <v>614</v>
+      </c>
+      <c r="C343" s="3" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>644</v>
+      </c>
+      <c r="B344" t="s">
+        <v>615</v>
+      </c>
+      <c r="C344" s="3" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>644</v>
+      </c>
+      <c r="B345" t="s">
+        <v>616</v>
+      </c>
+      <c r="C345" s="3" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>644</v>
+      </c>
+      <c r="B346" t="s">
+        <v>617</v>
+      </c>
+      <c r="C346" s="3" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>644</v>
+      </c>
+      <c r="B347" t="s">
+        <v>618</v>
+      </c>
+      <c r="C347" s="3" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>644</v>
+      </c>
+      <c r="B348" t="s">
+        <v>619</v>
+      </c>
+      <c r="C348" s="3" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>644</v>
+      </c>
+      <c r="B349" t="s">
+        <v>620</v>
+      </c>
+      <c r="C349" s="3" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>644</v>
+      </c>
+      <c r="B350" t="s">
+        <v>621</v>
+      </c>
+      <c r="C350" s="3" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>644</v>
+      </c>
+      <c r="B351" t="s">
+        <v>622</v>
+      </c>
+      <c r="C351" s="3" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>644</v>
+      </c>
+      <c r="B352" t="s">
+        <v>623</v>
+      </c>
+      <c r="C352" s="3" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>644</v>
+      </c>
+      <c r="B353" t="s">
+        <v>624</v>
+      </c>
+      <c r="C353" s="3" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>644</v>
+      </c>
+      <c r="B354" t="s">
+        <v>625</v>
+      </c>
+      <c r="C354" s="3" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>644</v>
+      </c>
+      <c r="B355" t="s">
+        <v>626</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>644</v>
+      </c>
+      <c r="B356" t="s">
+        <v>627</v>
+      </c>
+      <c r="C356" s="3" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>644</v>
+      </c>
+      <c r="B357" t="s">
+        <v>628</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>644</v>
+      </c>
+      <c r="B358" t="s">
+        <v>629</v>
+      </c>
+      <c r="C358" s="3" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>644</v>
+      </c>
+      <c r="B359" t="s">
+        <v>630</v>
+      </c>
+      <c r="C359" s="3" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>644</v>
+      </c>
+      <c r="B360" t="s">
+        <v>631</v>
+      </c>
+      <c r="C360" s="3" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>644</v>
+      </c>
+      <c r="B361" t="s">
+        <v>632</v>
+      </c>
+      <c r="C361" s="3" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>644</v>
+      </c>
+      <c r="B362" t="s">
+        <v>496</v>
+      </c>
+      <c r="C362" s="3" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>644</v>
+      </c>
+      <c r="B363" t="s">
+        <v>633</v>
+      </c>
+      <c r="C363" s="3" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>644</v>
+      </c>
+      <c r="B364" t="s">
+        <v>236</v>
+      </c>
+      <c r="C364" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>644</v>
+      </c>
+      <c r="B365" t="s">
+        <v>634</v>
+      </c>
+      <c r="C365" s="3" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>644</v>
+      </c>
+      <c r="B366" t="s">
+        <v>635</v>
+      </c>
+      <c r="C366" s="3" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>644</v>
+      </c>
+      <c r="B367" t="s">
+        <v>636</v>
+      </c>
+      <c r="C367" s="3" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>644</v>
+      </c>
+      <c r="B368" t="s">
+        <v>637</v>
+      </c>
+      <c r="C368" s="3" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>644</v>
+      </c>
+      <c r="B369" t="s">
+        <v>638</v>
+      </c>
+      <c r="C369" s="3" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>644</v>
+      </c>
+      <c r="B370" t="s">
+        <v>639</v>
+      </c>
+      <c r="C370" s="3" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>644</v>
+      </c>
+      <c r="B371" t="s">
+        <v>640</v>
+      </c>
+      <c r="C371" s="3" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>644</v>
+      </c>
+      <c r="B372" t="s">
+        <v>641</v>
+      </c>
+      <c r="C372" s="3" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>644</v>
+      </c>
+      <c r="B373" t="s">
+        <v>257</v>
+      </c>
+      <c r="C373" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>644</v>
+      </c>
+      <c r="B374" t="s">
+        <v>642</v>
+      </c>
+      <c r="C374" s="3" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>644</v>
+      </c>
+      <c r="B375" t="s">
+        <v>643</v>
+      </c>
+      <c r="C375" s="3" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>645</v>
+      </c>
+      <c r="B376" t="s">
+        <v>646</v>
+      </c>
+      <c r="C376" s="3" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>645</v>
+      </c>
+      <c r="B377" t="s">
+        <v>647</v>
+      </c>
+      <c r="C377" s="3" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>645</v>
+      </c>
+      <c r="B378" t="s">
+        <v>648</v>
+      </c>
+      <c r="C378" s="3" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>645</v>
+      </c>
+      <c r="B379" t="s">
+        <v>649</v>
+      </c>
+      <c r="C379" s="3" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>645</v>
+      </c>
+      <c r="B380" t="s">
+        <v>582</v>
+      </c>
+      <c r="C380" s="3" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>645</v>
+      </c>
+      <c r="B381" t="s">
+        <v>568</v>
+      </c>
+      <c r="C381" s="3" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>645</v>
+      </c>
+      <c r="B382" t="s">
+        <v>569</v>
+      </c>
+      <c r="C382" s="3" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>645</v>
+      </c>
+      <c r="B383" t="s">
+        <v>650</v>
+      </c>
+      <c r="C383" s="3" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>645</v>
+      </c>
+      <c r="B384" t="s">
+        <v>651</v>
+      </c>
+      <c r="C384" s="3" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>645</v>
+      </c>
+      <c r="B385" t="s">
+        <v>572</v>
+      </c>
+      <c r="C385" s="3" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>645</v>
+      </c>
+      <c r="B386" t="s">
+        <v>575</v>
+      </c>
+      <c r="C386" s="3" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>645</v>
+      </c>
+      <c r="B387" t="s">
+        <v>574</v>
+      </c>
+      <c r="C387" s="3" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>645</v>
+      </c>
+      <c r="B388" t="s">
+        <v>577</v>
+      </c>
+      <c r="C388" s="3" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>645</v>
+      </c>
+      <c r="B389" t="s">
+        <v>652</v>
+      </c>
+      <c r="C389" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>645</v>
+      </c>
+      <c r="B390" t="s">
+        <v>653</v>
+      </c>
+      <c r="C390" s="3" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>645</v>
+      </c>
+      <c r="B391" t="s">
+        <v>654</v>
+      </c>
+      <c r="C391" s="3" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>645</v>
+      </c>
+      <c r="B392" t="s">
+        <v>655</v>
+      </c>
+      <c r="C392" s="3" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>645</v>
+      </c>
+      <c r="B393" t="s">
+        <v>656</v>
+      </c>
+      <c r="C393" s="3" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>645</v>
+      </c>
+      <c r="B394" t="s">
+        <v>657</v>
+      </c>
+      <c r="C394" s="3" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>645</v>
+      </c>
+      <c r="B395" t="s">
+        <v>658</v>
+      </c>
+      <c r="C395" s="3" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>659</v>
+      </c>
+      <c r="B396" t="s">
+        <v>660</v>
+      </c>
+      <c r="C396" s="3" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>659</v>
+      </c>
+      <c r="B397" t="s">
+        <v>661</v>
+      </c>
+      <c r="C397" s="3" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>659</v>
+      </c>
+      <c r="B398" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C398" s="3" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>659</v>
+      </c>
+      <c r="B399" t="s">
+        <v>662</v>
+      </c>
+      <c r="C399" s="3" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>659</v>
+      </c>
+      <c r="B400" t="s">
+        <v>663</v>
+      </c>
+      <c r="C400" s="3" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>659</v>
+      </c>
+      <c r="B401" t="s">
+        <v>664</v>
+      </c>
+      <c r="C401" s="3" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>659</v>
+      </c>
+      <c r="B402" t="s">
+        <v>665</v>
+      </c>
+      <c r="C402" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>659</v>
+      </c>
+      <c r="B403" t="s">
+        <v>666</v>
+      </c>
+      <c r="C403" s="3" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>659</v>
+      </c>
+      <c r="B404" t="s">
+        <v>667</v>
+      </c>
+      <c r="C404" s="3" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>659</v>
+      </c>
+      <c r="B405" t="s">
+        <v>668</v>
+      </c>
+      <c r="C405" s="3" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>659</v>
+      </c>
+      <c r="B406" t="s">
+        <v>669</v>
+      </c>
+      <c r="C406" s="3" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>659</v>
+      </c>
+      <c r="B407" t="s">
+        <v>670</v>
+      </c>
+      <c r="C407" s="3" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>659</v>
+      </c>
+      <c r="B408" t="s">
+        <v>671</v>
+      </c>
+      <c r="C408" s="3" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>659</v>
+      </c>
+      <c r="B409" t="s">
+        <v>672</v>
+      </c>
+      <c r="C409" s="3" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>659</v>
+      </c>
+      <c r="B410" t="s">
+        <v>673</v>
+      </c>
+      <c r="C410" s="3" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>659</v>
+      </c>
+      <c r="B411" t="s">
+        <v>674</v>
+      </c>
+      <c r="C411" s="3" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>659</v>
+      </c>
+      <c r="B412" t="s">
+        <v>675</v>
+      </c>
+      <c r="C412" s="3" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>659</v>
+      </c>
+      <c r="B413" t="s">
+        <v>676</v>
+      </c>
+      <c r="C413" s="3" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>659</v>
+      </c>
+      <c r="B414" t="s">
+        <v>677</v>
+      </c>
+      <c r="C414" s="3" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>659</v>
+      </c>
+      <c r="B415" t="s">
+        <v>678</v>
+      </c>
+      <c r="C415" s="3" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>659</v>
+      </c>
+      <c r="B416" t="s">
+        <v>679</v>
+      </c>
+      <c r="C416" s="3" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>659</v>
+      </c>
+      <c r="B417" t="s">
+        <v>680</v>
+      </c>
+      <c r="C417" s="3" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>659</v>
+      </c>
+      <c r="B418" t="s">
+        <v>681</v>
+      </c>
+      <c r="C418" s="3" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>659</v>
+      </c>
+      <c r="B419" t="s">
+        <v>682</v>
+      </c>
+      <c r="C419" s="3" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>659</v>
+      </c>
+      <c r="B420" t="s">
+        <v>683</v>
+      </c>
+      <c r="C420" s="3" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>659</v>
+      </c>
+      <c r="B421" t="s">
+        <v>684</v>
+      </c>
+      <c r="C421" s="3" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>659</v>
+      </c>
+      <c r="B422" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C422" s="3" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>659</v>
+      </c>
+      <c r="B423" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C423" s="3" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>659</v>
+      </c>
+      <c r="B424" t="s">
+        <v>685</v>
+      </c>
+      <c r="C424" s="3" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>659</v>
+      </c>
+      <c r="B425" t="s">
+        <v>686</v>
+      </c>
+      <c r="C425" s="3" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>659</v>
+      </c>
+      <c r="B426" t="s">
+        <v>687</v>
+      </c>
+      <c r="C426" s="3" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>659</v>
+      </c>
+      <c r="B427" t="s">
+        <v>688</v>
+      </c>
+      <c r="C427" s="3" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>659</v>
+      </c>
+      <c r="B428" t="s">
+        <v>689</v>
+      </c>
+      <c r="C428" s="3" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>659</v>
+      </c>
+      <c r="B429" t="s">
+        <v>690</v>
+      </c>
+      <c r="C429" s="3" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>659</v>
+      </c>
+      <c r="B430" t="s">
+        <v>691</v>
+      </c>
+      <c r="C430" s="3" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>659</v>
+      </c>
+      <c r="B431" t="s">
+        <v>692</v>
+      </c>
+      <c r="C431" s="3" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>659</v>
+      </c>
+      <c r="B432" t="s">
+        <v>693</v>
+      </c>
+      <c r="C432" s="3" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>659</v>
+      </c>
+      <c r="B433" t="s">
+        <v>694</v>
+      </c>
+      <c r="C433" s="3" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>659</v>
+      </c>
+      <c r="B434" t="s">
+        <v>695</v>
+      </c>
+      <c r="C434" s="3" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>659</v>
+      </c>
+      <c r="B435" t="s">
+        <v>696</v>
+      </c>
+      <c r="C435" s="3" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>659</v>
+      </c>
+      <c r="B436" t="s">
+        <v>697</v>
+      </c>
+      <c r="C436" s="3" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>659</v>
+      </c>
+      <c r="B437" t="s">
+        <v>698</v>
+      </c>
+      <c r="C437" s="3" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>659</v>
+      </c>
+      <c r="B438" t="s">
+        <v>699</v>
+      </c>
+      <c r="C438" s="3" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>659</v>
+      </c>
+      <c r="B439" t="s">
+        <v>700</v>
+      </c>
+      <c r="C439" s="3" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>659</v>
+      </c>
+      <c r="B440" t="s">
+        <v>701</v>
+      </c>
+      <c r="C440" s="3" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>659</v>
+      </c>
+      <c r="B441" t="s">
+        <v>702</v>
+      </c>
+      <c r="C441" s="3" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>659</v>
+      </c>
+      <c r="B442" t="s">
+        <v>703</v>
+      </c>
+      <c r="C442" s="3" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>704</v>
+      </c>
+      <c r="B443" t="s">
+        <v>705</v>
+      </c>
+      <c r="C443" s="3" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>704</v>
+      </c>
+      <c r="B444" t="s">
+        <v>706</v>
+      </c>
+      <c r="C444" s="3" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>704</v>
+      </c>
+      <c r="B445" t="s">
+        <v>707</v>
+      </c>
+      <c r="C445" s="3" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>704</v>
+      </c>
+      <c r="B446" t="s">
+        <v>708</v>
+      </c>
+      <c r="C446" s="3" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>704</v>
+      </c>
+      <c r="B447" t="s">
+        <v>105</v>
+      </c>
+      <c r="C447" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>704</v>
+      </c>
+      <c r="B448" t="s">
+        <v>128</v>
+      </c>
+      <c r="C448" s="3" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>704</v>
+      </c>
+      <c r="B449" t="s">
+        <v>709</v>
+      </c>
+      <c r="C449" s="3" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>704</v>
+      </c>
+      <c r="B450" t="s">
+        <v>710</v>
+      </c>
+      <c r="C450" s="3" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>704</v>
+      </c>
+      <c r="B451" t="s">
+        <v>141</v>
+      </c>
+      <c r="C451" s="3" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>704</v>
+      </c>
+      <c r="B452" t="s">
+        <v>711</v>
+      </c>
+      <c r="C452" s="3" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>704</v>
+      </c>
+      <c r="B453" t="s">
+        <v>145</v>
+      </c>
+      <c r="C453" s="3" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>704</v>
+      </c>
+      <c r="B454" t="s">
+        <v>712</v>
+      </c>
+      <c r="C454" s="3" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>704</v>
+      </c>
+      <c r="B455" t="s">
+        <v>172</v>
+      </c>
+      <c r="C455" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>704</v>
+      </c>
+      <c r="B456" t="s">
+        <v>713</v>
+      </c>
+      <c r="C456" s="3" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>704</v>
+      </c>
+      <c r="B457" t="s">
+        <v>714</v>
+      </c>
+      <c r="C457" s="3" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>704</v>
+      </c>
+      <c r="B458" t="s">
+        <v>715</v>
+      </c>
+      <c r="C458" s="3" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>704</v>
+      </c>
+      <c r="B459" t="s">
+        <v>716</v>
+      </c>
+      <c r="C459" s="3" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>704</v>
+      </c>
+      <c r="B460" t="s">
+        <v>717</v>
+      </c>
+      <c r="C460" s="3" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>704</v>
+      </c>
+      <c r="B461" t="s">
+        <v>718</v>
+      </c>
+      <c r="C461" s="3" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>704</v>
+      </c>
+      <c r="B462" t="s">
+        <v>719</v>
+      </c>
+      <c r="C462" s="3" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>704</v>
+      </c>
+      <c r="B463" t="s">
+        <v>720</v>
+      </c>
+      <c r="C463" s="3" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>704</v>
+      </c>
+      <c r="B464" t="s">
+        <v>721</v>
+      </c>
+      <c r="C464" s="3" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>704</v>
+      </c>
+      <c r="B465" t="s">
+        <v>722</v>
+      </c>
+      <c r="C465" s="3" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>704</v>
+      </c>
+      <c r="B466" t="s">
+        <v>723</v>
+      </c>
+      <c r="C466" s="3" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>704</v>
+      </c>
+      <c r="B467" t="s">
+        <v>724</v>
+      </c>
+      <c r="C467" s="3" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>704</v>
+      </c>
+      <c r="B468" t="s">
+        <v>725</v>
+      </c>
+      <c r="C468" s="3" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>704</v>
+      </c>
+      <c r="B469" t="s">
+        <v>726</v>
+      </c>
+      <c r="C469" s="3" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>704</v>
+      </c>
+      <c r="B470" t="s">
+        <v>727</v>
+      </c>
+      <c r="C470" s="3" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>728</v>
+      </c>
+      <c r="B471" t="s">
+        <v>729</v>
+      </c>
+      <c r="C471" s="3" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>728</v>
+      </c>
+      <c r="B472" t="s">
+        <v>730</v>
+      </c>
+      <c r="C472" s="3" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>728</v>
+      </c>
+      <c r="B473" t="s">
+        <v>731</v>
+      </c>
+      <c r="C473" s="3" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>728</v>
+      </c>
+      <c r="B474" t="s">
+        <v>732</v>
+      </c>
+      <c r="C474" s="3" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>728</v>
+      </c>
+      <c r="B475" t="s">
+        <v>733</v>
+      </c>
+      <c r="C475" s="3" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>728</v>
+      </c>
+      <c r="B476" t="s">
+        <v>734</v>
+      </c>
+      <c r="C476" s="3" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>728</v>
+      </c>
+      <c r="B477" t="s">
+        <v>735</v>
+      </c>
+      <c r="C477" s="3" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>728</v>
+      </c>
+      <c r="B478" t="s">
+        <v>736</v>
+      </c>
+      <c r="C478" s="3" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>728</v>
+      </c>
+      <c r="B479" t="s">
+        <v>737</v>
+      </c>
+      <c r="C479" s="3" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>728</v>
+      </c>
+      <c r="B480" t="s">
+        <v>738</v>
+      </c>
+      <c r="C480" s="3" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>728</v>
+      </c>
+      <c r="B481" t="s">
+        <v>739</v>
+      </c>
+      <c r="C481" s="3" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>728</v>
+      </c>
+      <c r="B482" t="s">
+        <v>740</v>
+      </c>
+      <c r="C482" s="3" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>728</v>
+      </c>
+      <c r="B483" t="s">
+        <v>741</v>
+      </c>
+      <c r="C483" s="3" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>728</v>
+      </c>
+      <c r="B484" t="s">
+        <v>742</v>
+      </c>
+      <c r="C484" s="3" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>728</v>
+      </c>
+      <c r="B485" t="s">
+        <v>743</v>
+      </c>
+      <c r="C485" s="3" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>728</v>
+      </c>
+      <c r="B486" t="s">
+        <v>744</v>
+      </c>
+      <c r="C486" s="3" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>728</v>
+      </c>
+      <c r="B487" t="s">
+        <v>745</v>
+      </c>
+      <c r="C487" s="3" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>728</v>
+      </c>
+      <c r="B488" t="s">
+        <v>746</v>
+      </c>
+      <c r="C488" s="3" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>728</v>
+      </c>
+      <c r="B489" t="s">
+        <v>747</v>
+      </c>
+      <c r="C489" s="3" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>728</v>
+      </c>
+      <c r="B490" t="s">
+        <v>748</v>
+      </c>
+      <c r="C490" s="3" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>728</v>
+      </c>
+      <c r="B491" t="s">
+        <v>749</v>
+      </c>
+      <c r="C491" s="3" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>728</v>
+      </c>
+      <c r="B492" t="s">
+        <v>400</v>
+      </c>
+      <c r="C492" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>728</v>
+      </c>
+      <c r="B493" t="s">
+        <v>750</v>
+      </c>
+      <c r="C493" s="3" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>728</v>
+      </c>
+      <c r="B494" t="s">
+        <v>751</v>
+      </c>
+      <c r="C494" s="3" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>728</v>
+      </c>
+      <c r="B495" t="s">
+        <v>752</v>
+      </c>
+      <c r="C495" s="3" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>728</v>
+      </c>
+      <c r="B496" t="s">
+        <v>753</v>
+      </c>
+      <c r="C496" s="3" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>728</v>
+      </c>
+      <c r="B497" t="s">
+        <v>754</v>
+      </c>
+      <c r="C497" s="3" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>728</v>
+      </c>
+      <c r="B498" t="s">
+        <v>755</v>
+      </c>
+      <c r="C498" s="3" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>728</v>
+      </c>
+      <c r="B499" t="s">
+        <v>756</v>
+      </c>
+      <c r="C499" s="3" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>728</v>
+      </c>
+      <c r="B500" t="s">
+        <v>757</v>
+      </c>
+      <c r="C500" s="3" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>728</v>
+      </c>
+      <c r="B501" t="s">
+        <v>758</v>
+      </c>
+      <c r="C501" s="3" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>728</v>
+      </c>
+      <c r="B502" t="s">
+        <v>759</v>
+      </c>
+      <c r="C502" s="3" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>728</v>
+      </c>
+      <c r="B503" t="s">
+        <v>760</v>
+      </c>
+      <c r="C503" s="3" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>728</v>
+      </c>
+      <c r="B504" t="s">
+        <v>761</v>
+      </c>
+      <c r="C504" s="3" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>728</v>
+      </c>
+      <c r="B505" t="s">
+        <v>762</v>
+      </c>
+      <c r="C505" s="3" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>728</v>
+      </c>
+      <c r="B506" t="s">
+        <v>763</v>
+      </c>
+      <c r="C506" s="3" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
+        <v>728</v>
+      </c>
+      <c r="B507" t="s">
+        <v>764</v>
+      </c>
+      <c r="C507" s="3" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>728</v>
+      </c>
+      <c r="B508" t="s">
+        <v>188</v>
+      </c>
+      <c r="C508" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>728</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C509" s="3" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>728</v>
+      </c>
+      <c r="B510" t="s">
+        <v>765</v>
+      </c>
+      <c r="C510" s="3" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>728</v>
+      </c>
+      <c r="B511" t="s">
+        <v>766</v>
+      </c>
+      <c r="C511" s="3" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
+        <v>728</v>
+      </c>
+      <c r="B512" t="s">
+        <v>767</v>
+      </c>
+      <c r="C512" s="3" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
+        <v>728</v>
+      </c>
+      <c r="B513" t="s">
+        <v>768</v>
+      </c>
+      <c r="C513" s="3" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
+        <v>728</v>
+      </c>
+      <c r="B514" t="s">
+        <v>769</v>
+      </c>
+      <c r="C514" s="3" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>728</v>
+      </c>
+      <c r="B515" t="s">
+        <v>770</v>
+      </c>
+      <c r="C515" s="3" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>728</v>
+      </c>
+      <c r="B516" t="s">
+        <v>771</v>
+      </c>
+      <c r="C516" s="3" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
+        <v>728</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C517" s="3" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
+        <v>728</v>
+      </c>
+      <c r="B518" t="s">
+        <v>772</v>
+      </c>
+      <c r="C518" s="3" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A519" t="s">
+        <v>728</v>
+      </c>
+      <c r="B519" t="s">
+        <v>773</v>
+      </c>
+      <c r="C519" s="3" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A520" t="s">
+        <v>728</v>
+      </c>
+      <c r="B520" t="s">
+        <v>774</v>
+      </c>
+      <c r="C520" s="3" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
+        <v>728</v>
+      </c>
+      <c r="B521" t="s">
+        <v>775</v>
+      </c>
+      <c r="C521" s="3" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A522" t="s">
+        <v>728</v>
+      </c>
+      <c r="B522" t="s">
+        <v>776</v>
+      </c>
+      <c r="C522" s="3" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
+        <v>728</v>
+      </c>
+      <c r="B523" t="s">
+        <v>702</v>
+      </c>
+      <c r="C523" s="3" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
+        <v>728</v>
+      </c>
+      <c r="B524" t="s">
+        <v>777</v>
+      </c>
+      <c r="C524" s="3" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
+        <v>728</v>
+      </c>
+      <c r="B525" t="s">
+        <v>778</v>
+      </c>
+      <c r="C525" s="3" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
+        <v>728</v>
+      </c>
+      <c r="B526" t="s">
+        <v>779</v>
+      </c>
+      <c r="C526" s="3" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A527" t="s">
+        <v>728</v>
+      </c>
+      <c r="B527" t="s">
+        <v>780</v>
+      </c>
+      <c r="C527" s="3" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A528" t="s">
+        <v>728</v>
+      </c>
+      <c r="B528" t="s">
+        <v>781</v>
+      </c>
+      <c r="C528" s="3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
+        <v>728</v>
+      </c>
+      <c r="B529" t="s">
+        <v>782</v>
+      </c>
+      <c r="C529" s="3" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
+        <v>728</v>
+      </c>
+      <c r="B530" t="s">
+        <v>783</v>
+      </c>
+      <c r="C530" s="3" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
+        <v>728</v>
+      </c>
+      <c r="B531" t="s">
+        <v>784</v>
+      </c>
+      <c r="C531" s="3" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
+        <v>785</v>
+      </c>
+      <c r="B532" t="s">
+        <v>786</v>
+      </c>
+      <c r="C532" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A533" t="s">
+        <v>785</v>
+      </c>
+      <c r="B533" t="s">
+        <v>787</v>
+      </c>
+      <c r="C533" s="3" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A534" t="s">
+        <v>785</v>
+      </c>
+      <c r="B534" t="s">
+        <v>788</v>
+      </c>
+      <c r="C534" s="3" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A535" t="s">
+        <v>785</v>
+      </c>
+      <c r="B535" t="s">
+        <v>789</v>
+      </c>
+      <c r="C535" s="3" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A536" t="s">
+        <v>785</v>
+      </c>
+      <c r="B536" t="s">
+        <v>790</v>
+      </c>
+      <c r="C536" s="3" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A537" t="s">
+        <v>785</v>
+      </c>
+      <c r="B537" t="s">
+        <v>791</v>
+      </c>
+      <c r="C537" s="3" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A538" t="s">
+        <v>785</v>
+      </c>
+      <c r="B538" t="s">
+        <v>792</v>
+      </c>
+      <c r="C538" s="3" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A539" t="s">
+        <v>785</v>
+      </c>
+      <c r="B539" t="s">
+        <v>400</v>
+      </c>
+      <c r="C539" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A540" t="s">
+        <v>785</v>
+      </c>
+      <c r="B540" t="s">
+        <v>793</v>
+      </c>
+      <c r="C540" s="3" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A541" t="s">
+        <v>785</v>
+      </c>
+      <c r="B541" t="s">
+        <v>289</v>
+      </c>
+      <c r="C541" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A542" t="s">
+        <v>785</v>
+      </c>
+      <c r="B542" t="s">
+        <v>752</v>
+      </c>
+      <c r="C542" s="3" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A543" t="s">
+        <v>785</v>
+      </c>
+      <c r="B543" t="s">
+        <v>794</v>
+      </c>
+      <c r="C543" s="3" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A544" t="s">
+        <v>785</v>
+      </c>
+      <c r="B544" t="s">
+        <v>795</v>
+      </c>
+      <c r="C544" s="3" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A545" t="s">
+        <v>785</v>
+      </c>
+      <c r="B545" t="s">
+        <v>796</v>
+      </c>
+      <c r="C545" s="3" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A546" t="s">
+        <v>785</v>
+      </c>
+      <c r="B546" t="s">
+        <v>797</v>
+      </c>
+      <c r="C546" s="3" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A547" t="s">
+        <v>785</v>
+      </c>
+      <c r="B547" t="s">
+        <v>798</v>
+      </c>
+      <c r="C547" s="3" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A548" t="s">
+        <v>785</v>
+      </c>
+      <c r="B548" t="s">
+        <v>799</v>
+      </c>
+      <c r="C548" s="3" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
+        <v>785</v>
+      </c>
+      <c r="B549" t="s">
+        <v>800</v>
+      </c>
+      <c r="C549" s="3" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
+        <v>785</v>
+      </c>
+      <c r="B550" t="s">
+        <v>801</v>
+      </c>
+      <c r="C550" s="3" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A551" t="s">
+        <v>785</v>
+      </c>
+      <c r="B551" t="s">
+        <v>802</v>
+      </c>
+      <c r="C551" s="3" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A552" t="s">
+        <v>785</v>
+      </c>
+      <c r="B552" t="s">
+        <v>803</v>
+      </c>
+      <c r="C552" s="3" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A553" t="s">
+        <v>785</v>
+      </c>
+      <c r="B553" t="s">
+        <v>442</v>
+      </c>
+      <c r="C553" s="3" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
+        <v>785</v>
+      </c>
+      <c r="B554" t="s">
+        <v>644</v>
+      </c>
+      <c r="C554" s="3" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
+        <v>785</v>
+      </c>
+      <c r="B555" t="s">
+        <v>804</v>
+      </c>
+      <c r="C555" s="3" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
+        <v>785</v>
+      </c>
+      <c r="B556" t="s">
+        <v>514</v>
+      </c>
+      <c r="C556" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
+        <v>785</v>
+      </c>
+      <c r="B557" t="s">
+        <v>784</v>
+      </c>
+      <c r="C557" s="3" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
+        <v>785</v>
+      </c>
+      <c r="B558" t="s">
+        <v>805</v>
+      </c>
+      <c r="C558" s="3" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A559" t="s">
+        <v>785</v>
+      </c>
+      <c r="B559" t="s">
+        <v>806</v>
+      </c>
+      <c r="C559" s="3" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
+        <v>785</v>
+      </c>
+      <c r="B560" t="s">
+        <v>807</v>
+      </c>
+      <c r="C560" s="3" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
+        <v>785</v>
+      </c>
+      <c r="B561" t="s">
+        <v>744</v>
+      </c>
+      <c r="C561" s="3" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>785</v>
+      </c>
+      <c r="B562" t="s">
+        <v>808</v>
+      </c>
+      <c r="C562" s="3" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>785</v>
+      </c>
+      <c r="B563" t="s">
+        <v>188</v>
+      </c>
+      <c r="C563" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>785</v>
+      </c>
+      <c r="B564" t="s">
+        <v>765</v>
+      </c>
+      <c r="C564" s="3" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
+        <v>785</v>
+      </c>
+      <c r="B565" t="s">
+        <v>809</v>
+      </c>
+      <c r="C565" s="3" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A566" t="s">
+        <v>785</v>
+      </c>
+      <c r="B566" t="s">
+        <v>810</v>
+      </c>
+      <c r="C566" s="3" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
+        <v>785</v>
+      </c>
+      <c r="B567" t="s">
+        <v>811</v>
+      </c>
+      <c r="C567" s="3" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
+        <v>785</v>
+      </c>
+      <c r="B568" t="s">
+        <v>778</v>
+      </c>
+      <c r="C568" s="3" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
+        <v>785</v>
+      </c>
+      <c r="B569" t="s">
+        <v>812</v>
+      </c>
+      <c r="C569" s="3" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A570" t="s">
+        <v>785</v>
+      </c>
+      <c r="B570" t="s">
+        <v>813</v>
+      </c>
+      <c r="C570" s="3" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A571" t="s">
+        <v>785</v>
+      </c>
+      <c r="B571" t="s">
+        <v>814</v>
+      </c>
+      <c r="C571" s="3" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A572" t="s">
+        <v>785</v>
+      </c>
+      <c r="B572" t="s">
+        <v>815</v>
+      </c>
+      <c r="C572" s="3" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A573" t="s">
+        <v>785</v>
+      </c>
+      <c r="B573" t="s">
+        <v>129</v>
+      </c>
+      <c r="C573" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A574" t="s">
+        <v>785</v>
+      </c>
+      <c r="B574" t="s">
+        <v>160</v>
+      </c>
+      <c r="C574" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A575" t="s">
+        <v>785</v>
+      </c>
+      <c r="B575" t="s">
+        <v>616</v>
+      </c>
+      <c r="C575" s="3" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A576" t="s">
+        <v>785</v>
+      </c>
+      <c r="B576" t="s">
+        <v>816</v>
+      </c>
+      <c r="C576" s="3" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A577" t="s">
+        <v>785</v>
+      </c>
+      <c r="B577" t="s">
+        <v>172</v>
+      </c>
+      <c r="C577" s="3" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A578" t="s">
+        <v>785</v>
+      </c>
+      <c r="B578" t="s">
+        <v>817</v>
+      </c>
+      <c r="C578" s="3" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A579" t="s">
+        <v>785</v>
+      </c>
+      <c r="B579" t="s">
+        <v>295</v>
+      </c>
+      <c r="C579" s="3" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A580" t="s">
+        <v>785</v>
+      </c>
+      <c r="B580" t="s">
+        <v>818</v>
+      </c>
+      <c r="C580" s="3" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A581" t="s">
+        <v>785</v>
+      </c>
+      <c r="B581" t="s">
+        <v>236</v>
+      </c>
+      <c r="C581" s="3" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A582" t="s">
+        <v>785</v>
+      </c>
+      <c r="B582" t="s">
+        <v>819</v>
+      </c>
+      <c r="C582" s="3" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A583" t="s">
+        <v>785</v>
+      </c>
+      <c r="B583" t="s">
+        <v>820</v>
+      </c>
+      <c r="C583" s="3" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A584" t="s">
+        <v>785</v>
+      </c>
+      <c r="B584" t="s">
+        <v>821</v>
+      </c>
+      <c r="C584" s="3" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A585" t="s">
+        <v>785</v>
+      </c>
+      <c r="B585" t="s">
+        <v>257</v>
+      </c>
+      <c r="C585" s="3" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A586" t="s">
+        <v>785</v>
+      </c>
+      <c r="B586" t="s">
+        <v>822</v>
+      </c>
+      <c r="C586" s="3" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A587" t="s">
+        <v>785</v>
+      </c>
+      <c r="B587" t="s">
+        <v>823</v>
+      </c>
+      <c r="C587" s="3" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A588" t="s">
+        <v>785</v>
+      </c>
+      <c r="B588" t="s">
+        <v>824</v>
+      </c>
+      <c r="C588" s="3" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A589" t="s">
+        <v>785</v>
+      </c>
+      <c r="B589" t="s">
+        <v>825</v>
+      </c>
+      <c r="C589" s="3" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A590" t="s">
+        <v>785</v>
+      </c>
+      <c r="B590" t="s">
+        <v>826</v>
+      </c>
+      <c r="C590" s="3" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A591" t="s">
+        <v>785</v>
+      </c>
+      <c r="B591" t="s">
+        <v>827</v>
+      </c>
+      <c r="C591" s="3" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A592" t="s">
+        <v>785</v>
+      </c>
+      <c r="B592" t="s">
+        <v>828</v>
+      </c>
+      <c r="C592" s="3" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A593" t="s">
+        <v>785</v>
+      </c>
+      <c r="B593" t="s">
+        <v>829</v>
+      </c>
+      <c r="C593" s="3" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A594" t="s">
+        <v>785</v>
+      </c>
+      <c r="B594" t="s">
+        <v>830</v>
+      </c>
+      <c r="C594" s="3" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A595" t="s">
+        <v>785</v>
+      </c>
+      <c r="B595" t="s">
+        <v>831</v>
+      </c>
+      <c r="C595" s="3" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A596" t="s">
+        <v>785</v>
+      </c>
+      <c r="B596" t="s">
+        <v>832</v>
+      </c>
+      <c r="C596" s="3" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A597" t="s">
+        <v>785</v>
+      </c>
+      <c r="B597" t="s">
+        <v>833</v>
+      </c>
+      <c r="C597" s="3" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A598" t="s">
+        <v>785</v>
+      </c>
+      <c r="B598" t="s">
+        <v>63</v>
+      </c>
+      <c r="C598" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A599" t="s">
+        <v>785</v>
+      </c>
+      <c r="B599" t="s">
+        <v>61</v>
+      </c>
+      <c r="C599" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A600" t="s">
+        <v>785</v>
+      </c>
+      <c r="B600" t="s">
+        <v>64</v>
+      </c>
+      <c r="C600" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A601" t="s">
+        <v>785</v>
+      </c>
+      <c r="B601" t="s">
+        <v>834</v>
+      </c>
+      <c r="C601" s="3" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A602" t="s">
+        <v>785</v>
+      </c>
+      <c r="B602" t="s">
+        <v>835</v>
+      </c>
+      <c r="C602" s="3" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A603" t="s">
+        <v>785</v>
+      </c>
+      <c r="B603" t="s">
+        <v>836</v>
+      </c>
+      <c r="C603" s="3" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A604" t="s">
+        <v>785</v>
+      </c>
+      <c r="B604" t="s">
+        <v>837</v>
+      </c>
+      <c r="C604" s="3" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A605" t="s">
+        <v>785</v>
+      </c>
+      <c r="B605" t="s">
+        <v>838</v>
+      </c>
+      <c r="C605" s="3" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A606" t="s">
+        <v>785</v>
+      </c>
+      <c r="B606" t="s">
+        <v>839</v>
+      </c>
+      <c r="C606" s="3" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A607" t="s">
+        <v>785</v>
+      </c>
+      <c r="B607" t="s">
+        <v>840</v>
+      </c>
+      <c r="C607" s="3" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A608" t="s">
+        <v>785</v>
+      </c>
+      <c r="B608" t="s">
+        <v>841</v>
+      </c>
+      <c r="C608" s="3" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A609" t="s">
+        <v>785</v>
+      </c>
+      <c r="B609" t="s">
+        <v>842</v>
+      </c>
+      <c r="C609" s="3" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A610" t="s">
+        <v>785</v>
+      </c>
+      <c r="B610" t="s">
+        <v>198</v>
+      </c>
+      <c r="C610" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A611" t="s">
+        <v>785</v>
+      </c>
+      <c r="B611" t="s">
+        <v>843</v>
+      </c>
+      <c r="C611" s="3" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A612" t="s">
+        <v>785</v>
+      </c>
+      <c r="B612" t="s">
+        <v>844</v>
+      </c>
+      <c r="C612" s="3" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A613" t="s">
+        <v>785</v>
+      </c>
+      <c r="B613" t="s">
+        <v>845</v>
+      </c>
+      <c r="C613" s="3" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A614" t="s">
+        <v>785</v>
+      </c>
+      <c r="B614" t="s">
+        <v>846</v>
+      </c>
+      <c r="C614" s="3" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A615" t="s">
+        <v>785</v>
+      </c>
+      <c r="B615" t="s">
+        <v>847</v>
+      </c>
+      <c r="C615" s="3" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A616" t="s">
+        <v>785</v>
+      </c>
+      <c r="B616" t="s">
+        <v>848</v>
+      </c>
+      <c r="C616" s="3" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A617" t="s">
+        <v>785</v>
+      </c>
+      <c r="B617" t="s">
+        <v>849</v>
+      </c>
+      <c r="C617" s="3" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A618" t="s">
+        <v>785</v>
+      </c>
+      <c r="B618" t="s">
+        <v>850</v>
+      </c>
+      <c r="C618" s="3" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A619" t="s">
+        <v>785</v>
+      </c>
+      <c r="B619" t="s">
+        <v>851</v>
+      </c>
+      <c r="C619" s="3" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A620" t="s">
+        <v>785</v>
+      </c>
+      <c r="B620" t="s">
+        <v>740</v>
+      </c>
+      <c r="C620" s="3" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A621" t="s">
+        <v>785</v>
+      </c>
+      <c r="B621" t="s">
+        <v>852</v>
+      </c>
+      <c r="C621" s="3" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A622" t="s">
+        <v>785</v>
+      </c>
+      <c r="B622" t="s">
+        <v>853</v>
+      </c>
+      <c r="C622" s="3" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A623" t="s">
+        <v>785</v>
+      </c>
+      <c r="B623" t="s">
+        <v>854</v>
+      </c>
+      <c r="C623" s="3" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A624" t="s">
+        <v>785</v>
+      </c>
+      <c r="B624" t="s">
+        <v>855</v>
+      </c>
+      <c r="C624" s="3" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A625" t="s">
+        <v>785</v>
+      </c>
+      <c r="B625" t="s">
+        <v>856</v>
+      </c>
+      <c r="C625" s="3" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A626" t="s">
+        <v>785</v>
+      </c>
+      <c r="B626" t="s">
+        <v>857</v>
+      </c>
+      <c r="C626" s="3" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A627" t="s">
+        <v>785</v>
+      </c>
+      <c r="B627" t="s">
+        <v>858</v>
+      </c>
+      <c r="C627" s="3" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A628" t="s">
+        <v>785</v>
+      </c>
+      <c r="B628" t="s">
+        <v>859</v>
+      </c>
+      <c r="C628" s="3" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A629" t="s">
+        <v>785</v>
+      </c>
+      <c r="B629" t="s">
+        <v>772</v>
+      </c>
+      <c r="C629" s="3" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A630" t="s">
+        <v>785</v>
+      </c>
+      <c r="B630" t="s">
+        <v>775</v>
+      </c>
+      <c r="C630" s="3" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A631" t="s">
+        <v>785</v>
+      </c>
+      <c r="B631" t="s">
+        <v>860</v>
+      </c>
+      <c r="C631" s="3" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A632" t="s">
+        <v>785</v>
+      </c>
+      <c r="B632" t="s">
+        <v>779</v>
+      </c>
+      <c r="C632" s="3" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A633" t="s">
+        <v>785</v>
+      </c>
+      <c r="B633" t="s">
+        <v>861</v>
+      </c>
+      <c r="C633" s="3" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A634" t="s">
+        <v>855</v>
+      </c>
+      <c r="B634" t="s">
+        <v>862</v>
+      </c>
+      <c r="C634" s="3" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A635" t="s">
+        <v>855</v>
+      </c>
+      <c r="B635" t="s">
+        <v>863</v>
+      </c>
+      <c r="C635" s="3" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A636" t="s">
+        <v>855</v>
+      </c>
+      <c r="B636" t="s">
+        <v>864</v>
+      </c>
+      <c r="C636" s="3" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A637" t="s">
+        <v>855</v>
+      </c>
+      <c r="B637" t="s">
+        <v>851</v>
+      </c>
+      <c r="C637" s="3" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A638" t="s">
+        <v>855</v>
+      </c>
+      <c r="B638" t="s">
+        <v>787</v>
+      </c>
+      <c r="C638" s="3" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A639" t="s">
+        <v>855</v>
+      </c>
+      <c r="B639" t="s">
+        <v>865</v>
+      </c>
+      <c r="C639" s="3" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A640" t="s">
+        <v>855</v>
+      </c>
+      <c r="B640" t="s">
+        <v>866</v>
+      </c>
+      <c r="C640" s="3" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A641" t="s">
+        <v>855</v>
+      </c>
+      <c r="B641" t="s">
+        <v>867</v>
+      </c>
+      <c r="C641" s="3" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A642" t="s">
+        <v>855</v>
+      </c>
+      <c r="B642" t="s">
+        <v>868</v>
+      </c>
+      <c r="C642" s="3" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A643" t="s">
+        <v>855</v>
+      </c>
+      <c r="B643" t="s">
+        <v>644</v>
+      </c>
+      <c r="C643" s="3" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A644" t="s">
+        <v>855</v>
+      </c>
+      <c r="B644" t="s">
+        <v>869</v>
+      </c>
+      <c r="C644" s="3" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A645" t="s">
+        <v>855</v>
+      </c>
+      <c r="B645" t="s">
+        <v>236</v>
+      </c>
+      <c r="C645" s="3" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A646" t="s">
+        <v>855</v>
+      </c>
+      <c r="B646" t="s">
+        <v>870</v>
+      </c>
+      <c r="C646" s="3" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A647" t="s">
+        <v>855</v>
+      </c>
+      <c r="B647" t="s">
+        <v>871</v>
+      </c>
+      <c r="C647" s="3" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A648" t="s">
+        <v>872</v>
+      </c>
+      <c r="B648" t="s">
+        <v>873</v>
+      </c>
+      <c r="C648" s="3" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A649" t="s">
+        <v>872</v>
+      </c>
+      <c r="B649" t="s">
+        <v>874</v>
+      </c>
+      <c r="C649" s="3" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A650" t="s">
+        <v>872</v>
+      </c>
+      <c r="B650" t="s">
+        <v>875</v>
+      </c>
+      <c r="C650" s="3" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A651" t="s">
+        <v>872</v>
+      </c>
+      <c r="B651" t="s">
+        <v>876</v>
+      </c>
+      <c r="C651" s="3" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A652" t="s">
+        <v>872</v>
+      </c>
+      <c r="B652" t="s">
+        <v>877</v>
+      </c>
+      <c r="C652" s="3" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A653" t="s">
+        <v>872</v>
+      </c>
+      <c r="B653" t="s">
+        <v>878</v>
+      </c>
+      <c r="C653" s="3" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A654" t="s">
+        <v>872</v>
+      </c>
+      <c r="B654" t="s">
+        <v>879</v>
+      </c>
+      <c r="C654" s="3" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A655" t="s">
+        <v>872</v>
+      </c>
+      <c r="B655" t="s">
+        <v>880</v>
+      </c>
+      <c r="C655" s="3" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A656" t="s">
+        <v>872</v>
+      </c>
+      <c r="B656" t="s">
+        <v>881</v>
+      </c>
+      <c r="C656" s="3" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A657" t="s">
+        <v>872</v>
+      </c>
+      <c r="B657" t="s">
+        <v>864</v>
+      </c>
+      <c r="C657" s="3" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A658" t="s">
+        <v>872</v>
+      </c>
+      <c r="B658" t="s">
+        <v>882</v>
+      </c>
+      <c r="C658" s="3" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A659" t="s">
+        <v>872</v>
+      </c>
+      <c r="B659" t="s">
+        <v>883</v>
+      </c>
+      <c r="C659" s="3" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A660" t="s">
+        <v>872</v>
+      </c>
+      <c r="B660" t="s">
+        <v>884</v>
+      </c>
+      <c r="C660" s="3" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A661" t="s">
+        <v>872</v>
+      </c>
+      <c r="B661" t="s">
+        <v>885</v>
+      </c>
+      <c r="C661" s="3" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A662" t="s">
+        <v>872</v>
+      </c>
+      <c r="B662" t="s">
+        <v>886</v>
+      </c>
+      <c r="C662" s="3" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A663" t="s">
+        <v>872</v>
+      </c>
+      <c r="B663" t="s">
+        <v>887</v>
+      </c>
+      <c r="C663" s="3" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A664" t="s">
+        <v>872</v>
+      </c>
+      <c r="B664" t="s">
+        <v>888</v>
+      </c>
+      <c r="C664" s="3" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A665" t="s">
+        <v>872</v>
+      </c>
+      <c r="B665" t="s">
+        <v>889</v>
+      </c>
+      <c r="C665" s="3" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A666" t="s">
+        <v>872</v>
+      </c>
+      <c r="B666" t="s">
+        <v>890</v>
+      </c>
+      <c r="C666" s="3" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A667" t="s">
+        <v>872</v>
+      </c>
+      <c r="B667" t="s">
+        <v>891</v>
+      </c>
+      <c r="C667" s="3" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A668" t="s">
+        <v>872</v>
+      </c>
+      <c r="B668" t="s">
+        <v>892</v>
+      </c>
+      <c r="C668" s="3" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A669" t="s">
+        <v>872</v>
+      </c>
+      <c r="B669" t="s">
+        <v>893</v>
+      </c>
+      <c r="C669" s="3" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A670" t="s">
+        <v>872</v>
+      </c>
+      <c r="B670" t="s">
+        <v>894</v>
+      </c>
+      <c r="C670" s="3" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A671" t="s">
+        <v>872</v>
+      </c>
+      <c r="B671" t="s">
+        <v>895</v>
+      </c>
+      <c r="C671" s="3" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A672" t="s">
+        <v>872</v>
+      </c>
+      <c r="B672" t="s">
+        <v>896</v>
+      </c>
+      <c r="C672" s="3" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A673" t="s">
+        <v>872</v>
+      </c>
+      <c r="B673" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C673" s="3" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A674" t="s">
+        <v>872</v>
+      </c>
+      <c r="B674" t="s">
+        <v>897</v>
+      </c>
+      <c r="C674" s="3" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A675" t="s">
+        <v>872</v>
+      </c>
+      <c r="B675" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C675" s="3" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A676" t="s">
+        <v>872</v>
+      </c>
+      <c r="B676" t="s">
+        <v>898</v>
+      </c>
+      <c r="C676" s="3" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A677" t="s">
+        <v>872</v>
+      </c>
+      <c r="B677" t="s">
+        <v>899</v>
+      </c>
+      <c r="C677" s="3" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A678" t="s">
+        <v>872</v>
+      </c>
+      <c r="B678" t="s">
+        <v>900</v>
+      </c>
+      <c r="C678" s="3" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A679" t="s">
+        <v>872</v>
+      </c>
+      <c r="B679" t="s">
+        <v>901</v>
+      </c>
+      <c r="C679" s="3" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A680" t="s">
+        <v>872</v>
+      </c>
+      <c r="B680" t="s">
+        <v>902</v>
+      </c>
+      <c r="C680" s="3" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A681" t="s">
+        <v>872</v>
+      </c>
+      <c r="B681" t="s">
+        <v>903</v>
+      </c>
+      <c r="C681" s="3" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A682" t="s">
+        <v>872</v>
+      </c>
+      <c r="B682" t="s">
+        <v>904</v>
+      </c>
+      <c r="C682" s="3" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A683" t="s">
+        <v>872</v>
+      </c>
+      <c r="B683" t="s">
+        <v>14</v>
+      </c>
+      <c r="C683" s="3" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A684" t="s">
+        <v>872</v>
+      </c>
+      <c r="B684" t="s">
+        <v>905</v>
+      </c>
+      <c r="C684" s="3" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A685" t="s">
+        <v>872</v>
+      </c>
+      <c r="B685" t="s">
+        <v>906</v>
+      </c>
+      <c r="C685" s="3" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A686" t="s">
+        <v>872</v>
+      </c>
+      <c r="B686" t="s">
+        <v>907</v>
+      </c>
+      <c r="C686" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A687" t="s">
+        <v>872</v>
+      </c>
+      <c r="B687" t="s">
+        <v>908</v>
+      </c>
+      <c r="C687" s="3" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A688" t="s">
+        <v>872</v>
+      </c>
+      <c r="B688" t="s">
+        <v>909</v>
+      </c>
+      <c r="C688" s="3" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A689" t="s">
+        <v>872</v>
+      </c>
+      <c r="B689" t="s">
+        <v>910</v>
+      </c>
+      <c r="C689" s="3" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A690" t="s">
+        <v>872</v>
+      </c>
+      <c r="B690" t="s">
+        <v>911</v>
+      </c>
+      <c r="C690" s="3" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A691" t="s">
+        <v>872</v>
+      </c>
+      <c r="B691" t="s">
+        <v>912</v>
+      </c>
+      <c r="C691" s="3" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A692" t="s">
+        <v>872</v>
+      </c>
+      <c r="B692" t="s">
+        <v>913</v>
+      </c>
+      <c r="C692" s="3" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A693" t="s">
+        <v>872</v>
+      </c>
+      <c r="B693" t="s">
+        <v>914</v>
+      </c>
+      <c r="C693" s="3" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A694" t="s">
+        <v>872</v>
+      </c>
+      <c r="B694" t="s">
+        <v>915</v>
+      </c>
+      <c r="C694" s="3" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A695" t="s">
+        <v>872</v>
+      </c>
+      <c r="B695" t="s">
+        <v>916</v>
+      </c>
+      <c r="C695" s="3" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A696" t="s">
+        <v>872</v>
+      </c>
+      <c r="B696" t="s">
+        <v>917</v>
+      </c>
+      <c r="C696" s="3" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A697" t="s">
+        <v>872</v>
+      </c>
+      <c r="B697" t="s">
+        <v>918</v>
+      </c>
+      <c r="C697" s="3" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A698" t="s">
+        <v>872</v>
+      </c>
+      <c r="B698" t="s">
+        <v>919</v>
+      </c>
+      <c r="C698" s="3" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A699" t="s">
+        <v>872</v>
+      </c>
+      <c r="B699" t="s">
+        <v>920</v>
+      </c>
+      <c r="C699" s="3" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A700" t="s">
+        <v>872</v>
+      </c>
+      <c r="B700" t="s">
+        <v>921</v>
+      </c>
+      <c r="C700" s="3" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A701" t="s">
+        <v>872</v>
+      </c>
+      <c r="B701" t="s">
+        <v>922</v>
+      </c>
+      <c r="C701" s="3" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A702" t="s">
+        <v>872</v>
+      </c>
+      <c r="B702" t="s">
+        <v>923</v>
+      </c>
+      <c r="C702" s="3" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A703" t="s">
+        <v>872</v>
+      </c>
+      <c r="B703" t="s">
+        <v>924</v>
+      </c>
+      <c r="C703" s="3" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A704" t="s">
+        <v>872</v>
+      </c>
+      <c r="B704" t="s">
+        <v>925</v>
+      </c>
+      <c r="C704" s="3" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A705" t="s">
+        <v>872</v>
+      </c>
+      <c r="B705" t="s">
+        <v>926</v>
+      </c>
+      <c r="C705" s="3" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A706" t="s">
+        <v>872</v>
+      </c>
+      <c r="B706" t="s">
+        <v>927</v>
+      </c>
+      <c r="C706" s="3" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A707" t="s">
+        <v>872</v>
+      </c>
+      <c r="B707" t="s">
+        <v>928</v>
+      </c>
+      <c r="C707" s="3" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A708" t="s">
+        <v>872</v>
+      </c>
+      <c r="B708" t="s">
+        <v>929</v>
+      </c>
+      <c r="C708" s="3" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A709" t="s">
+        <v>872</v>
+      </c>
+      <c r="B709" t="s">
+        <v>930</v>
+      </c>
+      <c r="C709" s="3" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A710" t="s">
+        <v>872</v>
+      </c>
+      <c r="B710" t="s">
+        <v>931</v>
+      </c>
+      <c r="C710" s="3" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A711" t="s">
+        <v>872</v>
+      </c>
+      <c r="B711" t="s">
+        <v>932</v>
+      </c>
+      <c r="C711" s="3" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A712" t="s">
+        <v>872</v>
+      </c>
+      <c r="B712" t="s">
+        <v>933</v>
+      </c>
+      <c r="C712" s="3" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A713" t="s">
+        <v>872</v>
+      </c>
+      <c r="B713" t="s">
+        <v>934</v>
+      </c>
+      <c r="C713" s="3" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A714" t="s">
+        <v>872</v>
+      </c>
+      <c r="B714" t="s">
+        <v>935</v>
+      </c>
+      <c r="C714" s="3" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A715" t="s">
+        <v>872</v>
+      </c>
+      <c r="B715" t="s">
+        <v>936</v>
+      </c>
+      <c r="C715" s="3" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A716" t="s">
+        <v>872</v>
+      </c>
+      <c r="B716" t="s">
+        <v>937</v>
+      </c>
+      <c r="C716" s="3" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A717" t="s">
+        <v>872</v>
+      </c>
+      <c r="B717" t="s">
+        <v>938</v>
+      </c>
+      <c r="C717" s="3" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A718" t="s">
+        <v>872</v>
+      </c>
+      <c r="B718" t="s">
+        <v>939</v>
+      </c>
+      <c r="C718" s="3" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="719" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A719" t="s">
+        <v>872</v>
+      </c>
+      <c r="B719" t="s">
+        <v>940</v>
+      </c>
+      <c r="C719" s="3" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="720" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A720" t="s">
+        <v>872</v>
+      </c>
+      <c r="B720" t="s">
+        <v>941</v>
+      </c>
+      <c r="C720" s="3" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="721" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A721" t="s">
+        <v>872</v>
+      </c>
+      <c r="B721" t="s">
+        <v>942</v>
+      </c>
+      <c r="C721" s="3" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="722" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A722" t="s">
+        <v>872</v>
+      </c>
+      <c r="B722" t="s">
+        <v>943</v>
+      </c>
+      <c r="C722" s="3" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A723" t="s">
+        <v>872</v>
+      </c>
+      <c r="B723" t="s">
+        <v>944</v>
+      </c>
+      <c r="C723" s="3" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A724" t="s">
+        <v>872</v>
+      </c>
+      <c r="B724" t="s">
+        <v>43</v>
+      </c>
+      <c r="C724" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="725" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A725" t="s">
+        <v>872</v>
+      </c>
+      <c r="B725" t="s">
+        <v>945</v>
+      </c>
+      <c r="C725" s="3" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="726" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A726" t="s">
+        <v>872</v>
+      </c>
+      <c r="B726" t="s">
+        <v>946</v>
+      </c>
+      <c r="C726" s="3" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="727" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A727" t="s">
+        <v>872</v>
+      </c>
+      <c r="B727" t="s">
+        <v>947</v>
+      </c>
+      <c r="C727" s="3" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="728" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A728" t="s">
+        <v>872</v>
+      </c>
+      <c r="B728" t="s">
+        <v>948</v>
+      </c>
+      <c r="C728" s="3" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="729" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A729" t="s">
+        <v>872</v>
+      </c>
+      <c r="B729" t="s">
+        <v>949</v>
+      </c>
+      <c r="C729" s="3" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="730" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A730" t="s">
+        <v>872</v>
+      </c>
+      <c r="B730" t="s">
+        <v>868</v>
+      </c>
+      <c r="C730" s="3" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="731" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A731" t="s">
+        <v>872</v>
+      </c>
+      <c r="B731" t="s">
+        <v>950</v>
+      </c>
+      <c r="C731" s="3" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="732" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A732" t="s">
+        <v>872</v>
+      </c>
+      <c r="B732" t="s">
+        <v>951</v>
+      </c>
+      <c r="C732" s="3" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="733" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A733" t="s">
+        <v>872</v>
+      </c>
+      <c r="B733" t="s">
+        <v>952</v>
+      </c>
+      <c r="C733" s="3" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="734" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A734" t="s">
+        <v>872</v>
+      </c>
+      <c r="B734" t="s">
+        <v>953</v>
+      </c>
+      <c r="C734" s="3" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="735" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A735" t="s">
+        <v>872</v>
+      </c>
+      <c r="B735" t="s">
+        <v>954</v>
+      </c>
+      <c r="C735" s="3" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="736" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A736" t="s">
+        <v>872</v>
+      </c>
+      <c r="B736" t="s">
+        <v>955</v>
+      </c>
+      <c r="C736" s="3" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="737" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A737" t="s">
+        <v>872</v>
+      </c>
+      <c r="B737" t="s">
+        <v>956</v>
+      </c>
+      <c r="C737" s="3" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="738" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A738" t="s">
+        <v>872</v>
+      </c>
+      <c r="B738" t="s">
+        <v>957</v>
+      </c>
+      <c r="C738" s="3" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="739" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A739" t="s">
+        <v>872</v>
+      </c>
+      <c r="B739" t="s">
+        <v>958</v>
+      </c>
+      <c r="C739" s="3" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="740" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A740" t="s">
+        <v>872</v>
+      </c>
+      <c r="B740" t="s">
+        <v>959</v>
+      </c>
+      <c r="C740" s="3" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="741" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A741" t="s">
+        <v>872</v>
+      </c>
+      <c r="B741" t="s">
+        <v>960</v>
+      </c>
+      <c r="C741" s="3" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="742" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A742" t="s">
+        <v>872</v>
+      </c>
+      <c r="B742" t="s">
+        <v>961</v>
+      </c>
+      <c r="C742" s="3" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="743" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A743" t="s">
+        <v>872</v>
+      </c>
+      <c r="B743" t="s">
+        <v>962</v>
+      </c>
+      <c r="C743" s="3" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="744" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A744" t="s">
+        <v>872</v>
+      </c>
+      <c r="B744" t="s">
+        <v>963</v>
+      </c>
+      <c r="C744" s="3" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="745" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A745" t="s">
+        <v>872</v>
+      </c>
+      <c r="B745" t="s">
+        <v>964</v>
+      </c>
+      <c r="C745" s="3" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="746" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A746" t="s">
+        <v>872</v>
+      </c>
+      <c r="B746" t="s">
+        <v>965</v>
+      </c>
+      <c r="C746" s="3" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="747" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A747" t="s">
+        <v>872</v>
+      </c>
+      <c r="B747" t="s">
+        <v>966</v>
+      </c>
+      <c r="C747" s="3" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="748" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A748" t="s">
+        <v>872</v>
+      </c>
+      <c r="B748" t="s">
+        <v>967</v>
+      </c>
+      <c r="C748" s="3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="749" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A749" t="s">
+        <v>872</v>
+      </c>
+      <c r="B749" t="s">
+        <v>968</v>
+      </c>
+      <c r="C749" s="3" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="750" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A750" t="s">
+        <v>872</v>
+      </c>
+      <c r="B750" t="s">
+        <v>969</v>
+      </c>
+      <c r="C750" s="3" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="751" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A751" t="s">
+        <v>872</v>
+      </c>
+      <c r="B751" t="s">
+        <v>499</v>
+      </c>
+      <c r="C751" s="3" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="752" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A752" t="s">
+        <v>872</v>
+      </c>
+      <c r="B752" t="s">
+        <v>970</v>
+      </c>
+      <c r="C752" s="3" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="753" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A753" t="s">
+        <v>872</v>
+      </c>
+      <c r="B753" t="s">
+        <v>971</v>
+      </c>
+      <c r="C753" s="3" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="754" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A754" t="s">
+        <v>872</v>
+      </c>
+      <c r="B754" t="s">
+        <v>972</v>
+      </c>
+      <c r="C754" s="3" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="755" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A755" t="s">
+        <v>872</v>
+      </c>
+      <c r="B755" t="s">
+        <v>973</v>
+      </c>
+      <c r="C755" s="3" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="756" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A756" t="s">
+        <v>872</v>
+      </c>
+      <c r="B756" t="s">
+        <v>974</v>
+      </c>
+      <c r="C756" s="3" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="757" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A757" t="s">
+        <v>872</v>
+      </c>
+      <c r="B757" t="s">
+        <v>975</v>
+      </c>
+      <c r="C757" s="3" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="758" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A758" t="s">
+        <v>872</v>
+      </c>
+      <c r="B758" t="s">
+        <v>976</v>
+      </c>
+      <c r="C758" s="3" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="759" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A759" t="s">
+        <v>872</v>
+      </c>
+      <c r="B759" t="s">
+        <v>977</v>
+      </c>
+      <c r="C759" s="3" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="760" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A760" t="s">
+        <v>872</v>
+      </c>
+      <c r="B760" t="s">
+        <v>978</v>
+      </c>
+      <c r="C760" s="3" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="761" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A761" t="s">
+        <v>872</v>
+      </c>
+      <c r="B761" t="s">
+        <v>979</v>
+      </c>
+      <c r="C761" s="3" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="762" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A762" t="s">
+        <v>872</v>
+      </c>
+      <c r="B762" t="s">
+        <v>980</v>
+      </c>
+      <c r="C762" s="3" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="763" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A763" t="s">
+        <v>872</v>
+      </c>
+      <c r="B763" t="s">
+        <v>981</v>
+      </c>
+      <c r="C763" s="3" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="764" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A764" t="s">
+        <v>872</v>
+      </c>
+      <c r="B764" t="s">
+        <v>982</v>
+      </c>
+      <c r="C764" s="3" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="765" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A765" t="s">
+        <v>872</v>
+      </c>
+      <c r="B765" t="s">
+        <v>983</v>
+      </c>
+      <c r="C765" s="3" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="766" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A766" t="s">
+        <v>872</v>
+      </c>
+      <c r="B766" t="s">
+        <v>984</v>
+      </c>
+      <c r="C766" s="3" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="767" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A767" t="s">
+        <v>872</v>
+      </c>
+      <c r="B767" t="s">
+        <v>985</v>
+      </c>
+      <c r="C767" s="3" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="768" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A768" t="s">
+        <v>872</v>
+      </c>
+      <c r="B768" t="s">
+        <v>986</v>
+      </c>
+      <c r="C768" s="3" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="769" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A769" t="s">
+        <v>872</v>
+      </c>
+      <c r="B769" t="s">
+        <v>987</v>
+      </c>
+      <c r="C769" s="3" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="770" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A770" t="s">
+        <v>872</v>
+      </c>
+      <c r="B770" t="s">
+        <v>988</v>
+      </c>
+      <c r="C770" s="3" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="771" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A771" t="s">
+        <v>872</v>
+      </c>
+      <c r="B771" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C771" s="3" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="772" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A772" t="s">
+        <v>872</v>
+      </c>
+      <c r="B772" t="s">
+        <v>989</v>
+      </c>
+      <c r="C772" s="3" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A773" t="s">
+        <v>872</v>
+      </c>
+      <c r="B773" t="s">
+        <v>990</v>
+      </c>
+      <c r="C773" s="3" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="774" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A774" t="s">
+        <v>872</v>
+      </c>
+      <c r="B774" t="s">
+        <v>991</v>
+      </c>
+      <c r="C774" s="3" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="775" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A775" t="s">
+        <v>872</v>
+      </c>
+      <c r="B775" t="s">
+        <v>992</v>
+      </c>
+      <c r="C775" s="3" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A776" t="s">
+        <v>872</v>
+      </c>
+      <c r="B776" t="s">
+        <v>993</v>
+      </c>
+      <c r="C776" s="3" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A777" t="s">
+        <v>872</v>
+      </c>
+      <c r="B777" t="s">
+        <v>994</v>
+      </c>
+      <c r="C777" s="3" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="778" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A778" t="s">
+        <v>872</v>
+      </c>
+      <c r="B778" t="s">
+        <v>995</v>
+      </c>
+      <c r="C778" s="3" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="779" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A779" t="s">
+        <v>872</v>
+      </c>
+      <c r="B779" t="s">
+        <v>996</v>
+      </c>
+      <c r="C779" s="3" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="780" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A780" t="s">
+        <v>872</v>
+      </c>
+      <c r="B780" t="s">
+        <v>997</v>
+      </c>
+      <c r="C780" s="3" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="781" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A781" t="s">
+        <v>872</v>
+      </c>
+      <c r="B781" t="s">
+        <v>998</v>
+      </c>
+      <c r="C781" s="3" t="s">
+        <v>1129</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:A781" xr:uid="{B2645F77-54E4-4B19-94FC-FC73E6D10C88}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5586,15 +13568,15 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DE91823-2918-4C2B-A4F9-421DF1AF4FDE}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2b96267d-f15a-4e2d-a0c2-6fa6303eca79"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="2b96267d-f15a-4e2d-a0c2-6fa6303eca79"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>